--- a/Docs/report/TEAM_1_Project Status Report.xlsx
+++ b/Docs/report/TEAM_1_Project Status Report.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA-Project\QA-project-tool\Docs\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A5EDD5-D2BB-4690-94FF-73CBD7E6F336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3539A87F-D063-47CA-9A59-8F5C9C2FFA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release#1" sheetId="1" r:id="rId1"/>
     <sheet name="Release#2" sheetId="2" r:id="rId2"/>
     <sheet name="Release#3" sheetId="4" r:id="rId3"/>
     <sheet name="Release#4" sheetId="3" r:id="rId4"/>
+    <sheet name="Release#5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,14 +35,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="3Ua4wsPVU2+OjJeWbmtYzx5bg+lUiDntYAmcCMaFM74="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="3Ua4wsPVU2+OjJeWbmtYzx5bg+lUiDntYAmcCMaFM74="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="128">
   <si>
     <t>Day</t>
   </si>
@@ -425,6 +426,18 @@
   </si>
   <si>
     <t>lack of team members due to illnes</t>
+  </si>
+  <si>
+    <t>backend development1</t>
+  </si>
+  <si>
+    <t>backend development2</t>
+  </si>
+  <si>
+    <t>continue front development 1</t>
+  </si>
+  <si>
+    <t>continue front development 2</t>
   </si>
 </sst>
 </file>
@@ -868,7 +881,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1088,25 +1101,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1120,12 +1131,26 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3166,6 +3191,734 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-6FE9-479D-AF38-9962CB2B10FC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="2028298865"/>
+        <c:axId val="517339348"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2028298865"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="517339348"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="517339348"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr sz="900" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2028298865"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr sz="900" b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Planned</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="4285F4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Release#5'!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Release#5'!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A9FB-4840-8A6B-081AD16780F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Consumed</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="EA4335"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Release#5'!$A$2:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Release#5'!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A9FB-4840-8A6B-081AD16780F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="759985173"/>
+        <c:axId val="398362538"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="759985173"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="398362538"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="398362538"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="759985173"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0" i="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[TEAM_1_Project Status Report.xlsx]Release#5!Release#3</c:name>
+    <c:fmtId val="2"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="8.4701895161049923E-2"/>
+          <c:y val="5.8479532163742687E-2"/>
+          <c:w val="0.74860068676487246"/>
+          <c:h val="0.79150097465886937"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Release#5'!$Q$4:$Q$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Hours</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Release#5'!$P$6:$P$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>abdalrahman</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>alaaa</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>alhussin</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>nabil</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>zahraan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Release#5'!$Q$6:$Q$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-27E8-4D4C-BC0C-4E8D0968ACC2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Release#5'!$R$4:$R$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Done</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Release#5'!$P$6:$P$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>abdalrahman</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>alaaa</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>alhussin</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>nabil</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>zahraan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Release#5'!$R$6:$R$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-27E8-4D4C-BC0C-4E8D0968ACC2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3530,6 +4283,77 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B4FB73D-306B-4107-B738-2493F758EDC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1251857</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>217714</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7549243" cy="2677886"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1" title="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33F76CC8-30FA-4124-99D7-59CAFB430D91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>4118</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>98338</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="6709720" cy="3257550"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{775B1C2F-8CB5-4C3E-9C61-C9C624F147F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4116,6 +4940,110 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4D24A4A-83E6-4F38-BF99-7949CBE850DD}" name="Release#3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
+  <location ref="P4:R11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField name="Deliverable" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="% Completed" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField name="Comments" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
+      <items count="6">
+        <item x="4"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField name="Done" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Hours" fld="3" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Done" fld="4" baseField="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="1" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -4498,15 +5426,15 @@
       <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="91"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="95"/>
       <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4756,15 +5684,15 @@
       <c r="I26" s="10"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="89" t="s">
+      <c r="A27" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="90"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="91"/>
+      <c r="B27" s="94"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="95"/>
       <c r="I27" s="10"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7242,15 +8170,15 @@
       <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="89" t="s">
+      <c r="A13" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="90"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="91"/>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="95"/>
       <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7332,15 +8260,15 @@
       <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="89" t="s">
+      <c r="A21" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="91"/>
+      <c r="B21" s="94"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="95"/>
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9998,15 +10926,15 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="98" t="s">
+      <c r="A12" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
       <c r="I12" s="35" t="s">
         <v>82</v>
       </c>
@@ -10401,15 +11329,15 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="99"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="99"/>
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
       <c r="I28" s="35" t="s">
         <v>66</v>
       </c>
@@ -10665,7 +11593,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="100">
+      <c r="N43" s="98">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -10679,7 +11607,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="95">
+      <c r="R43" s="101">
         <f>SUM(O43:O50)</f>
         <v>24</v>
       </c>
@@ -10689,7 +11617,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="101"/>
+      <c r="N44" s="99"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O71" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>3</v>
@@ -10701,14 +11629,14 @@
         <f t="shared" ref="Q44:Q71" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alaaa</v>
       </c>
-      <c r="R44" s="95"/>
+      <c r="R44" s="101"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="101"/>
+      <c r="N45" s="99"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10720,14 +11648,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R45" s="95"/>
+      <c r="R45" s="101"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="101"/>
+      <c r="N46" s="99"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10739,14 +11667,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R46" s="95"/>
+      <c r="R46" s="101"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="101"/>
+      <c r="N47" s="99"/>
       <c r="O47" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10758,14 +11686,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R47" s="95"/>
+      <c r="R47" s="101"/>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="101"/>
+      <c r="N48" s="99"/>
       <c r="O48" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10777,14 +11705,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R48" s="95"/>
+      <c r="R48" s="101"/>
     </row>
     <row r="49" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="101"/>
+      <c r="N49" s="99"/>
       <c r="O49" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10796,14 +11724,14 @@
         <f t="shared" si="1"/>
         <v>Boda</v>
       </c>
-      <c r="R49" s="95"/>
+      <c r="R49" s="101"/>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
-      <c r="N50" s="102"/>
+      <c r="N50" s="100"/>
       <c r="O50" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10815,14 +11743,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R50" s="103"/>
+      <c r="R50" s="102"/>
     </row>
     <row r="51" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="100">
+      <c r="N51" s="98">
         <v>2</v>
       </c>
       <c r="O51" s="25">
@@ -10836,7 +11764,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R51" s="104">
+      <c r="R51" s="103">
         <f>SUM(O51:O52)</f>
         <v>4</v>
       </c>
@@ -10846,7 +11774,7 @@
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="101"/>
+      <c r="N52" s="99"/>
       <c r="O52" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -10858,7 +11786,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R52" s="104"/>
+      <c r="R52" s="103"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
@@ -10889,7 +11817,7 @@
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="92">
+      <c r="N54" s="104">
         <v>4</v>
       </c>
       <c r="O54" s="25">
@@ -10903,7 +11831,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R54" s="94">
+      <c r="R54" s="106">
         <f>SUM(O54:O61)</f>
         <v>8</v>
       </c>
@@ -10913,7 +11841,7 @@
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="93"/>
+      <c r="N55" s="105"/>
       <c r="O55" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -10925,14 +11853,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R55" s="95"/>
+      <c r="R55" s="101"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="93"/>
+      <c r="N56" s="105"/>
       <c r="O56" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -10944,14 +11872,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R56" s="95"/>
+      <c r="R56" s="101"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="93"/>
+      <c r="N57" s="105"/>
       <c r="O57" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -10963,14 +11891,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R57" s="95"/>
+      <c r="R57" s="101"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="93"/>
+      <c r="N58" s="105"/>
       <c r="O58" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -10982,14 +11910,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R58" s="95"/>
+      <c r="R58" s="101"/>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="93"/>
+      <c r="N59" s="105"/>
       <c r="O59" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11001,14 +11929,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R59" s="95"/>
+      <c r="R59" s="101"/>
     </row>
     <row r="60" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="93"/>
+      <c r="N60" s="105"/>
       <c r="O60" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11020,14 +11948,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R60" s="95"/>
+      <c r="R60" s="101"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="93"/>
+      <c r="N61" s="105"/>
       <c r="O61" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11039,14 +11967,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R61" s="96"/>
+      <c r="R61" s="107"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="92">
+      <c r="N62" s="104">
         <v>5</v>
       </c>
       <c r="O62" s="25">
@@ -11060,7 +11988,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R62" s="94">
+      <c r="R62" s="106">
         <f>SUM(O62:O66)</f>
         <v>12</v>
       </c>
@@ -11070,7 +11998,7 @@
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="93"/>
+      <c r="N63" s="105"/>
       <c r="O63" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -11082,14 +12010,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R63" s="93"/>
+      <c r="R63" s="105"/>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="93"/>
+      <c r="N64" s="105"/>
       <c r="O64" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -11101,14 +12029,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R64" s="93"/>
+      <c r="R64" s="105"/>
     </row>
     <row r="65" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="93"/>
+      <c r="N65" s="105"/>
       <c r="O65" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -11120,14 +12048,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R65" s="93"/>
+      <c r="R65" s="105"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="97"/>
+      <c r="N66" s="108"/>
       <c r="O66" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11139,14 +12067,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R66" s="97"/>
+      <c r="R66" s="108"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="92">
+      <c r="N67" s="104">
         <v>6</v>
       </c>
       <c r="O67" s="25">
@@ -11160,7 +12088,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R67" s="94">
+      <c r="R67" s="106">
         <f>SUM(O67:O71)</f>
         <v>12</v>
       </c>
@@ -11170,7 +12098,7 @@
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="93"/>
+      <c r="N68" s="105"/>
       <c r="O68" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -11182,14 +12110,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R68" s="93"/>
+      <c r="R68" s="105"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
-      <c r="N69" s="93"/>
+      <c r="N69" s="105"/>
       <c r="O69" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -11201,14 +12129,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R69" s="93"/>
+      <c r="R69" s="105"/>
     </row>
     <row r="70" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="21"/>
       <c r="B70" s="21"/>
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
-      <c r="N70" s="93"/>
+      <c r="N70" s="105"/>
       <c r="O70" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -11220,14 +12148,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R70" s="93"/>
+      <c r="R70" s="105"/>
     </row>
     <row r="71" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="21"/>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
-      <c r="N71" s="97"/>
+      <c r="N71" s="108"/>
       <c r="O71" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11239,7 +12167,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R71" s="97"/>
+      <c r="R71" s="108"/>
     </row>
     <row r="72" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
@@ -12211,18 +13139,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N54:N61"/>
+    <mergeCell ref="R54:R61"/>
+    <mergeCell ref="N62:N66"/>
+    <mergeCell ref="R62:R66"/>
+    <mergeCell ref="N67:N71"/>
+    <mergeCell ref="R67:R71"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="N43:N50"/>
     <mergeCell ref="R43:R50"/>
     <mergeCell ref="N51:N52"/>
     <mergeCell ref="R51:R52"/>
-    <mergeCell ref="N54:N61"/>
-    <mergeCell ref="R54:R61"/>
-    <mergeCell ref="N62:N66"/>
-    <mergeCell ref="R62:R66"/>
-    <mergeCell ref="N67:N71"/>
-    <mergeCell ref="R67:R71"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F14:F25 F30:F40" xr:uid="{AFC4AC33-7B9C-40BD-80E0-C1F9CEEBC5BF}">
@@ -12616,15 +13544,15 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="98" t="s">
+      <c r="A12" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
       <c r="I12" s="35" t="s">
         <v>121</v>
       </c>
@@ -12873,15 +13801,15 @@
       <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="99"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="99"/>
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
       <c r="I28" s="35"/>
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
@@ -13105,7 +14033,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="100">
+      <c r="N43" s="98">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -13119,7 +14047,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="95">
+      <c r="R43" s="101">
         <f>SUM(O43:O47)</f>
         <v>15</v>
       </c>
@@ -13129,7 +14057,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="101"/>
+      <c r="N44" s="99"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O68" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>3</v>
@@ -13141,14 +14069,14 @@
         <f t="shared" ref="Q44:Q68" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alaaa</v>
       </c>
-      <c r="R44" s="95"/>
+      <c r="R44" s="101"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="101"/>
+      <c r="N45" s="99"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -13160,14 +14088,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R45" s="95"/>
+      <c r="R45" s="101"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="101"/>
+      <c r="N46" s="99"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -13179,14 +14107,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R46" s="95"/>
+      <c r="R46" s="101"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="101"/>
+      <c r="N47" s="99"/>
       <c r="O47" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -13198,14 +14126,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R47" s="95"/>
+      <c r="R47" s="101"/>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="100">
+      <c r="N48" s="98">
         <v>2</v>
       </c>
       <c r="O48" s="25">
@@ -13219,7 +14147,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R48" s="104">
+      <c r="R48" s="103">
         <f>SUM(O48:O49)</f>
         <v>6</v>
       </c>
@@ -13229,7 +14157,7 @@
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="101"/>
+      <c r="N49" s="99"/>
       <c r="O49" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -13241,7 +14169,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R49" s="104"/>
+      <c r="R49" s="103"/>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
@@ -13269,7 +14197,7 @@
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="92">
+      <c r="N51" s="104">
         <v>4</v>
       </c>
       <c r="O51" s="25" t="e">
@@ -13281,7 +14209,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R51" s="94">
+      <c r="R51" s="106">
         <v>0</v>
       </c>
     </row>
@@ -13290,7 +14218,7 @@
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="93"/>
+      <c r="N52" s="105"/>
       <c r="O52" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13300,14 +14228,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R52" s="95"/>
+      <c r="R52" s="101"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
-      <c r="N53" s="93"/>
+      <c r="N53" s="105"/>
       <c r="O53" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13317,14 +14245,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R53" s="95"/>
+      <c r="R53" s="101"/>
     </row>
     <row r="54" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="93"/>
+      <c r="N54" s="105"/>
       <c r="O54" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13334,14 +14262,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R54" s="95"/>
+      <c r="R54" s="101"/>
     </row>
     <row r="55" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="93"/>
+      <c r="N55" s="105"/>
       <c r="O55" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13351,14 +14279,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R55" s="95"/>
+      <c r="R55" s="101"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="93"/>
+      <c r="N56" s="105"/>
       <c r="O56" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13368,14 +14296,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R56" s="95"/>
+      <c r="R56" s="101"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="93"/>
+      <c r="N57" s="105"/>
       <c r="O57" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13385,14 +14313,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R57" s="95"/>
+      <c r="R57" s="101"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="93"/>
+      <c r="N58" s="105"/>
       <c r="O58" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13402,14 +14330,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R58" s="96"/>
+      <c r="R58" s="107"/>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="92">
+      <c r="N59" s="104">
         <v>5</v>
       </c>
       <c r="O59" s="25" t="e">
@@ -13421,7 +14349,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R59" s="94">
+      <c r="R59" s="106">
         <v>0</v>
       </c>
     </row>
@@ -13430,7 +14358,7 @@
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="93"/>
+      <c r="N60" s="105"/>
       <c r="O60" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13440,14 +14368,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R60" s="93"/>
+      <c r="R60" s="105"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="93"/>
+      <c r="N61" s="105"/>
       <c r="O61" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13457,14 +14385,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R61" s="93"/>
+      <c r="R61" s="105"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="93"/>
+      <c r="N62" s="105"/>
       <c r="O62" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13474,14 +14402,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R62" s="93"/>
+      <c r="R62" s="105"/>
     </row>
     <row r="63" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="97"/>
+      <c r="N63" s="108"/>
       <c r="O63" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -13491,14 +14419,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R63" s="97"/>
+      <c r="R63" s="108"/>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="92">
+      <c r="N64" s="104">
         <v>6</v>
       </c>
       <c r="O64" s="25">
@@ -13512,7 +14440,7 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R64" s="94">
+      <c r="R64" s="106">
         <f>SUM(O64:O68)</f>
         <v>29</v>
       </c>
@@ -13522,7 +14450,7 @@
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="93"/>
+      <c r="N65" s="105"/>
       <c r="O65" s="25">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -13534,14 +14462,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R65" s="93"/>
+      <c r="R65" s="105"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="93"/>
+      <c r="N66" s="105"/>
       <c r="O66" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -13553,14 +14481,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R66" s="93"/>
+      <c r="R66" s="105"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="93"/>
+      <c r="N67" s="105"/>
       <c r="O67" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -13572,14 +14500,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R67" s="93"/>
+      <c r="R67" s="105"/>
     </row>
     <row r="68" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="97"/>
+      <c r="N68" s="108"/>
       <c r="O68" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -13591,7 +14519,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R68" s="97"/>
+      <c r="R68" s="108"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
@@ -14563,6 +15491,9 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="R51:R58"/>
+    <mergeCell ref="R59:R63"/>
     <mergeCell ref="R64:R68"/>
     <mergeCell ref="N51:N58"/>
     <mergeCell ref="N59:N63"/>
@@ -14572,9 +15503,6 @@
     <mergeCell ref="R48:R49"/>
     <mergeCell ref="R43:R47"/>
     <mergeCell ref="N43:N47"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="R51:R58"/>
-    <mergeCell ref="R59:R63"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <dataValidations count="1">
@@ -14586,4 +15514,2281 @@
   <pageSetup orientation="portrait"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44FB87AA-73A7-447D-A9F5-CCC196DD52C8}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:AB228"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="25.8" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.77734375" style="20" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" style="20" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" style="20" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="73.44140625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="10" style="20" customWidth="1"/>
+    <col min="7" max="7" width="60.77734375" style="20" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="20"/>
+    <col min="9" max="9" width="59.44140625" style="20" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="20" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" style="20" customWidth="1"/>
+    <col min="12" max="13" width="12.6640625" style="20"/>
+    <col min="14" max="14" width="16.109375" style="20" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" style="20" customWidth="1"/>
+    <col min="16" max="16" width="47.109375" style="20" customWidth="1"/>
+    <col min="17" max="17" width="27" style="20" customWidth="1"/>
+    <col min="18" max="18" width="23.5546875" style="20" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" style="20"/>
+    <col min="20" max="20" width="8.88671875" style="20" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" style="20"/>
+    <col min="22" max="22" width="64.44140625" style="20" customWidth="1"/>
+    <col min="23" max="24" width="12.6640625" style="20"/>
+    <col min="25" max="25" width="75" style="20" customWidth="1"/>
+    <col min="26" max="16384" width="12.6640625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="91" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="91" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="76" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="91" t="s">
+        <v>111</v>
+      </c>
+      <c r="M1" s="91" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="66">
+        <v>1</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="73">
+        <v>50</v>
+      </c>
+      <c r="I2" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" s="43">
+        <v>1</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="72">
+        <v>3</v>
+      </c>
+      <c r="M2" s="71"/>
+    </row>
+    <row r="3" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="66">
+        <v>2</v>
+      </c>
+      <c r="B3" s="74"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="21"/>
+      <c r="I3" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="43">
+        <v>0</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="L3" s="22">
+        <v>8</v>
+      </c>
+      <c r="M3" s="22"/>
+    </row>
+    <row r="4" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="66">
+        <v>3</v>
+      </c>
+      <c r="B4" s="74"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="21"/>
+      <c r="I4" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="J4" s="43">
+        <v>0</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="22">
+        <v>8</v>
+      </c>
+      <c r="M4" s="22"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="R4" s="79"/>
+    </row>
+    <row r="5" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="66">
+        <v>4</v>
+      </c>
+      <c r="B5" s="74"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="21"/>
+      <c r="I5" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" s="43">
+        <v>1</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="L5" s="22">
+        <v>2</v>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="P5" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="R5" s="80" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB5" s="69"/>
+    </row>
+    <row r="6" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="66">
+        <v>5</v>
+      </c>
+      <c r="B6" s="74"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="21"/>
+      <c r="I6" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" s="43">
+        <v>1</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L6" s="22">
+        <v>2</v>
+      </c>
+      <c r="M6" s="22"/>
+      <c r="P6" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q6" s="81">
+        <v>11</v>
+      </c>
+      <c r="R6" s="82">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="66">
+        <v>6</v>
+      </c>
+      <c r="B7" s="65"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="21"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="43">
+        <v>1</v>
+      </c>
+      <c r="K7" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="P7" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q7" s="84">
+        <v>11</v>
+      </c>
+      <c r="R7" s="85">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="43">
+        <v>1</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="P8" s="83" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q8" s="84">
+        <v>11</v>
+      </c>
+      <c r="R8" s="85">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="43">
+        <v>1</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="P9" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9" s="84">
+        <v>6</v>
+      </c>
+      <c r="R9" s="85">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="43">
+        <v>1</v>
+      </c>
+      <c r="K10" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="P10" s="83" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="84">
+        <v>11</v>
+      </c>
+      <c r="R10" s="85">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="43">
+        <v>1</v>
+      </c>
+      <c r="K11" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="P11" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="87">
+        <v>50</v>
+      </c>
+      <c r="R11" s="88">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="97"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="97"/>
+      <c r="G12" s="97"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="43">
+        <v>1</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+    </row>
+    <row r="13" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="35"/>
+      <c r="J13" s="43">
+        <v>1</v>
+      </c>
+      <c r="K13" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+    </row>
+    <row r="14" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="37"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+    </row>
+    <row r="15" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="56"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+    </row>
+    <row r="16" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="29"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+    </row>
+    <row r="17" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="29"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+    </row>
+    <row r="18" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="36"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+    </row>
+    <row r="19" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+    </row>
+    <row r="20" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+    </row>
+    <row r="21" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+    </row>
+    <row r="22" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+    </row>
+    <row r="23" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="32"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+    </row>
+    <row r="24" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+    </row>
+    <row r="25" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="32"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+    </row>
+    <row r="26" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+    </row>
+    <row r="27" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+    </row>
+    <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="96" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="97"/>
+      <c r="C28" s="97"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="97"/>
+      <c r="G28" s="97"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+    </row>
+    <row r="29" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="35"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="22"/>
+    </row>
+    <row r="30" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="41">
+        <v>1</v>
+      </c>
+      <c r="B30" s="52"/>
+      <c r="C30" s="90">
+        <v>5</v>
+      </c>
+      <c r="D30" s="50">
+        <v>5</v>
+      </c>
+      <c r="E30" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" s="47"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+    </row>
+    <row r="31" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="41"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="45"/>
+      <c r="G31" s="44"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+    </row>
+    <row r="32" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="41"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="42"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+    </row>
+    <row r="33" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="41"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="29"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+    </row>
+    <row r="34" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="32"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="36"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+    </row>
+    <row r="35" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="32"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="22"/>
+    </row>
+    <row r="36" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="22"/>
+    </row>
+    <row r="37" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="K37" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="L37" s="22">
+        <f>SUM(L2:L36)</f>
+        <v>23</v>
+      </c>
+      <c r="M37" s="22">
+        <f>SUM(M2:M36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="32"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+    </row>
+    <row r="39" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="32"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+    </row>
+    <row r="40" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="32"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+    </row>
+    <row r="41" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+    </row>
+    <row r="42" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="N42" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="O42" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="P42" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q42" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="R42" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="N43" s="98">
+        <v>1</v>
+      </c>
+      <c r="O43" s="25">
+        <f>VLOOKUP(P43,$I$2:$L$36,4,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="P43" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q43" s="24" t="str">
+        <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
+        <v>nabil</v>
+      </c>
+      <c r="R43" s="101" t="e">
+        <f>SUM(O43:O47)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="N44" s="99"/>
+      <c r="O44" s="25" t="e">
+        <f t="shared" ref="O44:O68" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="P44" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q44" s="24" t="e">
+        <f t="shared" ref="Q44:Q68" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="R44" s="101"/>
+    </row>
+    <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="N45" s="99"/>
+      <c r="O45" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P45" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q45" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R45" s="101"/>
+    </row>
+    <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="N46" s="99"/>
+      <c r="O46" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P46" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q46" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R46" s="101"/>
+    </row>
+    <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="N47" s="99"/>
+      <c r="O47" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P47" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q47" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R47" s="101"/>
+    </row>
+    <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="N48" s="98">
+        <v>2</v>
+      </c>
+      <c r="O48" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P48" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q48" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R48" s="103" t="e">
+        <f>SUM(O48:O49)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="N49" s="99"/>
+      <c r="O49" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P49" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q49" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R49" s="103"/>
+    </row>
+    <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="N50" s="92">
+        <v>3</v>
+      </c>
+      <c r="O50" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P50" s="24"/>
+      <c r="Q50" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R50" s="89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="21"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="N51" s="104">
+        <v>4</v>
+      </c>
+      <c r="O51" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P51" s="24"/>
+      <c r="Q51" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R51" s="106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="21"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="N52" s="105"/>
+      <c r="O52" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P52" s="24"/>
+      <c r="Q52" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R52" s="101"/>
+    </row>
+    <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="N53" s="105"/>
+      <c r="O53" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P53" s="24"/>
+      <c r="Q53" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R53" s="101"/>
+    </row>
+    <row r="54" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="N54" s="105"/>
+      <c r="O54" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P54" s="24"/>
+      <c r="Q54" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R54" s="101"/>
+    </row>
+    <row r="55" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="21"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="N55" s="105"/>
+      <c r="O55" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P55" s="24"/>
+      <c r="Q55" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R55" s="101"/>
+    </row>
+    <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="21"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="N56" s="105"/>
+      <c r="O56" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P56" s="24"/>
+      <c r="Q56" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R56" s="101"/>
+    </row>
+    <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="21"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="N57" s="105"/>
+      <c r="O57" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P57" s="24"/>
+      <c r="Q57" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R57" s="101"/>
+    </row>
+    <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="21"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="N58" s="105"/>
+      <c r="O58" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P58" s="24"/>
+      <c r="Q58" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R58" s="107"/>
+    </row>
+    <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="21"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="N59" s="104">
+        <v>5</v>
+      </c>
+      <c r="O59" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P59" s="24"/>
+      <c r="Q59" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R59" s="106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="21"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="N60" s="105"/>
+      <c r="O60" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P60" s="24"/>
+      <c r="Q60" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R60" s="105"/>
+    </row>
+    <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="21"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="N61" s="105"/>
+      <c r="O61" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R61" s="105"/>
+    </row>
+    <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="21"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="N62" s="105"/>
+      <c r="O62" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P62" s="24"/>
+      <c r="Q62" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R62" s="105"/>
+    </row>
+    <row r="63" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="21"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="N63" s="108"/>
+      <c r="O63" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P63" s="24"/>
+      <c r="Q63" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R63" s="108"/>
+    </row>
+    <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="21"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="N64" s="104">
+        <v>6</v>
+      </c>
+      <c r="O64" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P64" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q64" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R64" s="106" t="e">
+        <f>SUM(O64:O68)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="21"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="N65" s="105"/>
+      <c r="O65" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P65" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q65" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R65" s="105"/>
+    </row>
+    <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="21"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="N66" s="105"/>
+      <c r="O66" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P66" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q66" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R66" s="105"/>
+    </row>
+    <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="21"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="N67" s="105"/>
+      <c r="O67" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P67" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q67" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R67" s="105"/>
+    </row>
+    <row r="68" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="21"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="N68" s="108"/>
+      <c r="O68" s="25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P68" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q68" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R68" s="108"/>
+    </row>
+    <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="21"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="P69" s="24"/>
+      <c r="Q69" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="R69" s="22" t="e">
+        <f>SUM(R43:R68)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="21"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+    </row>
+    <row r="71" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="21"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+    </row>
+    <row r="72" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="21"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+    </row>
+    <row r="73" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="21"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+    </row>
+    <row r="74" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="21"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+    </row>
+    <row r="75" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="21"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+    </row>
+    <row r="76" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="21"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+    </row>
+    <row r="77" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="21"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+    </row>
+    <row r="78" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="21"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+    </row>
+    <row r="79" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="21"/>
+      <c r="B79" s="21"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+    </row>
+    <row r="80" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="21"/>
+      <c r="B80" s="21"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+    </row>
+    <row r="81" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="21"/>
+      <c r="B81" s="21"/>
+      <c r="C81" s="21"/>
+      <c r="D81" s="21"/>
+    </row>
+    <row r="82" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="21"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+    </row>
+    <row r="83" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="21"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
+    </row>
+    <row r="84" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="21"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="21"/>
+    </row>
+    <row r="85" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="21"/>
+      <c r="B85" s="21"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
+    </row>
+    <row r="86" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="21"/>
+      <c r="B86" s="21"/>
+      <c r="C86" s="21"/>
+      <c r="D86" s="21"/>
+    </row>
+    <row r="87" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="21"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+    </row>
+    <row r="88" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="21"/>
+      <c r="B88" s="21"/>
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
+    </row>
+    <row r="89" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="21"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="21"/>
+    </row>
+    <row r="90" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="21"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
+    </row>
+    <row r="91" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="21"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
+    </row>
+    <row r="92" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="21"/>
+      <c r="B92" s="21"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
+    </row>
+    <row r="93" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="21"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="21"/>
+      <c r="D93" s="21"/>
+    </row>
+    <row r="94" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="21"/>
+      <c r="B94" s="21"/>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+    </row>
+    <row r="95" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="21"/>
+      <c r="B95" s="21"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
+    </row>
+    <row r="96" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="21"/>
+      <c r="B96" s="21"/>
+      <c r="C96" s="21"/>
+      <c r="D96" s="21"/>
+    </row>
+    <row r="97" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="21"/>
+      <c r="B97" s="21"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+    </row>
+    <row r="98" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="21"/>
+      <c r="B98" s="21"/>
+      <c r="C98" s="21"/>
+      <c r="D98" s="21"/>
+    </row>
+    <row r="99" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="21"/>
+      <c r="B99" s="21"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+    </row>
+    <row r="100" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="21"/>
+      <c r="B100" s="21"/>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
+    </row>
+    <row r="101" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="21"/>
+      <c r="B101" s="21"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+    </row>
+    <row r="102" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="21"/>
+      <c r="B102" s="21"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+    </row>
+    <row r="103" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="21"/>
+      <c r="B103" s="21"/>
+      <c r="C103" s="21"/>
+      <c r="D103" s="21"/>
+    </row>
+    <row r="104" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="21"/>
+      <c r="B104" s="21"/>
+      <c r="C104" s="21"/>
+      <c r="D104" s="21"/>
+    </row>
+    <row r="105" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="21"/>
+      <c r="B105" s="21"/>
+      <c r="C105" s="21"/>
+      <c r="D105" s="21"/>
+    </row>
+    <row r="106" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="21"/>
+      <c r="B106" s="21"/>
+      <c r="C106" s="21"/>
+      <c r="D106" s="21"/>
+    </row>
+    <row r="107" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="21"/>
+      <c r="B107" s="21"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
+    </row>
+    <row r="108" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="21"/>
+      <c r="B108" s="21"/>
+      <c r="C108" s="21"/>
+      <c r="D108" s="21"/>
+    </row>
+    <row r="109" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="21"/>
+      <c r="B109" s="21"/>
+      <c r="C109" s="21"/>
+      <c r="D109" s="21"/>
+    </row>
+    <row r="110" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="21"/>
+      <c r="B110" s="21"/>
+      <c r="C110" s="21"/>
+      <c r="D110" s="21"/>
+    </row>
+    <row r="111" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="21"/>
+      <c r="B111" s="21"/>
+      <c r="C111" s="21"/>
+      <c r="D111" s="21"/>
+    </row>
+    <row r="112" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="21"/>
+      <c r="B112" s="21"/>
+      <c r="C112" s="21"/>
+      <c r="D112" s="21"/>
+    </row>
+    <row r="113" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="21"/>
+      <c r="B113" s="21"/>
+      <c r="C113" s="21"/>
+      <c r="D113" s="21"/>
+    </row>
+    <row r="114" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="21"/>
+      <c r="B114" s="21"/>
+      <c r="C114" s="21"/>
+      <c r="D114" s="21"/>
+    </row>
+    <row r="115" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="21"/>
+      <c r="B115" s="21"/>
+      <c r="C115" s="21"/>
+      <c r="D115" s="21"/>
+    </row>
+    <row r="116" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="21"/>
+      <c r="B116" s="21"/>
+      <c r="C116" s="21"/>
+      <c r="D116" s="21"/>
+    </row>
+    <row r="117" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="21"/>
+      <c r="B117" s="21"/>
+      <c r="C117" s="21"/>
+      <c r="D117" s="21"/>
+    </row>
+    <row r="118" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="21"/>
+      <c r="B118" s="21"/>
+      <c r="C118" s="21"/>
+      <c r="D118" s="21"/>
+    </row>
+    <row r="119" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="21"/>
+      <c r="B119" s="21"/>
+      <c r="C119" s="21"/>
+      <c r="D119" s="21"/>
+    </row>
+    <row r="120" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="21"/>
+      <c r="B120" s="21"/>
+      <c r="C120" s="21"/>
+      <c r="D120" s="21"/>
+    </row>
+    <row r="121" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="21"/>
+      <c r="B121" s="21"/>
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
+    </row>
+    <row r="122" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="21"/>
+      <c r="B122" s="21"/>
+      <c r="C122" s="21"/>
+      <c r="D122" s="21"/>
+    </row>
+    <row r="123" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="21"/>
+      <c r="B123" s="21"/>
+      <c r="C123" s="21"/>
+      <c r="D123" s="21"/>
+    </row>
+    <row r="124" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="21"/>
+      <c r="B124" s="21"/>
+      <c r="C124" s="21"/>
+      <c r="D124" s="21"/>
+    </row>
+    <row r="125" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="21"/>
+      <c r="B125" s="21"/>
+      <c r="C125" s="21"/>
+      <c r="D125" s="21"/>
+    </row>
+    <row r="126" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="21"/>
+      <c r="B126" s="21"/>
+      <c r="C126" s="21"/>
+      <c r="D126" s="21"/>
+    </row>
+    <row r="127" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="21"/>
+      <c r="B127" s="21"/>
+      <c r="C127" s="21"/>
+      <c r="D127" s="21"/>
+    </row>
+    <row r="128" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="21"/>
+      <c r="B128" s="21"/>
+      <c r="C128" s="21"/>
+      <c r="D128" s="21"/>
+    </row>
+    <row r="129" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="21"/>
+      <c r="B129" s="21"/>
+      <c r="C129" s="21"/>
+      <c r="D129" s="21"/>
+    </row>
+    <row r="130" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="21"/>
+      <c r="B130" s="21"/>
+      <c r="C130" s="21"/>
+      <c r="D130" s="21"/>
+    </row>
+    <row r="131" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="21"/>
+      <c r="B131" s="21"/>
+      <c r="C131" s="21"/>
+      <c r="D131" s="21"/>
+    </row>
+    <row r="132" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="21"/>
+      <c r="B132" s="21"/>
+      <c r="C132" s="21"/>
+      <c r="D132" s="21"/>
+    </row>
+    <row r="133" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="21"/>
+      <c r="B133" s="21"/>
+      <c r="C133" s="21"/>
+      <c r="D133" s="21"/>
+    </row>
+    <row r="134" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="21"/>
+      <c r="B134" s="21"/>
+      <c r="C134" s="21"/>
+      <c r="D134" s="21"/>
+    </row>
+    <row r="135" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="21"/>
+      <c r="B135" s="21"/>
+      <c r="C135" s="21"/>
+      <c r="D135" s="21"/>
+    </row>
+    <row r="136" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="21"/>
+      <c r="B136" s="21"/>
+      <c r="C136" s="21"/>
+      <c r="D136" s="21"/>
+    </row>
+    <row r="137" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="21"/>
+      <c r="B137" s="21"/>
+      <c r="C137" s="21"/>
+      <c r="D137" s="21"/>
+    </row>
+    <row r="138" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="21"/>
+      <c r="B138" s="21"/>
+      <c r="C138" s="21"/>
+      <c r="D138" s="21"/>
+    </row>
+    <row r="139" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="21"/>
+      <c r="B139" s="21"/>
+      <c r="C139" s="21"/>
+      <c r="D139" s="21"/>
+    </row>
+    <row r="140" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="21"/>
+      <c r="B140" s="21"/>
+      <c r="C140" s="21"/>
+      <c r="D140" s="21"/>
+    </row>
+    <row r="141" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="21"/>
+      <c r="B141" s="21"/>
+      <c r="C141" s="21"/>
+      <c r="D141" s="21"/>
+    </row>
+    <row r="142" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="21"/>
+      <c r="B142" s="21"/>
+      <c r="C142" s="21"/>
+      <c r="D142" s="21"/>
+    </row>
+    <row r="143" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="21"/>
+      <c r="B143" s="21"/>
+      <c r="C143" s="21"/>
+      <c r="D143" s="21"/>
+    </row>
+    <row r="144" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="21"/>
+      <c r="B144" s="21"/>
+      <c r="C144" s="21"/>
+      <c r="D144" s="21"/>
+    </row>
+    <row r="145" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="21"/>
+      <c r="B145" s="21"/>
+      <c r="C145" s="21"/>
+      <c r="D145" s="21"/>
+    </row>
+    <row r="146" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="21"/>
+      <c r="B146" s="21"/>
+      <c r="C146" s="21"/>
+      <c r="D146" s="21"/>
+    </row>
+    <row r="147" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="21"/>
+      <c r="B147" s="21"/>
+      <c r="C147" s="21"/>
+      <c r="D147" s="21"/>
+    </row>
+    <row r="148" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="21"/>
+      <c r="B148" s="21"/>
+      <c r="C148" s="21"/>
+      <c r="D148" s="21"/>
+    </row>
+    <row r="149" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="21"/>
+      <c r="B149" s="21"/>
+      <c r="C149" s="21"/>
+      <c r="D149" s="21"/>
+    </row>
+    <row r="150" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="21"/>
+      <c r="B150" s="21"/>
+      <c r="C150" s="21"/>
+      <c r="D150" s="21"/>
+    </row>
+    <row r="151" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="21"/>
+      <c r="B151" s="21"/>
+      <c r="C151" s="21"/>
+      <c r="D151" s="21"/>
+    </row>
+    <row r="152" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="21"/>
+      <c r="B152" s="21"/>
+      <c r="C152" s="21"/>
+      <c r="D152" s="21"/>
+    </row>
+    <row r="153" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="21"/>
+      <c r="B153" s="21"/>
+      <c r="C153" s="21"/>
+      <c r="D153" s="21"/>
+    </row>
+    <row r="154" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="21"/>
+      <c r="B154" s="21"/>
+      <c r="C154" s="21"/>
+      <c r="D154" s="21"/>
+    </row>
+    <row r="155" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="21"/>
+      <c r="B155" s="21"/>
+      <c r="C155" s="21"/>
+      <c r="D155" s="21"/>
+    </row>
+    <row r="156" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="21"/>
+      <c r="B156" s="21"/>
+      <c r="C156" s="21"/>
+      <c r="D156" s="21"/>
+    </row>
+    <row r="157" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="21"/>
+      <c r="B157" s="21"/>
+      <c r="C157" s="21"/>
+      <c r="D157" s="21"/>
+    </row>
+    <row r="158" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="21"/>
+      <c r="B158" s="21"/>
+      <c r="C158" s="21"/>
+      <c r="D158" s="21"/>
+    </row>
+    <row r="159" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="21"/>
+      <c r="B159" s="21"/>
+      <c r="C159" s="21"/>
+      <c r="D159" s="21"/>
+    </row>
+    <row r="160" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="21"/>
+      <c r="B160" s="21"/>
+      <c r="C160" s="21"/>
+      <c r="D160" s="21"/>
+    </row>
+    <row r="161" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="21"/>
+      <c r="B161" s="21"/>
+      <c r="C161" s="21"/>
+      <c r="D161" s="21"/>
+    </row>
+    <row r="162" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="21"/>
+      <c r="B162" s="21"/>
+      <c r="C162" s="21"/>
+      <c r="D162" s="21"/>
+    </row>
+    <row r="163" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="21"/>
+      <c r="B163" s="21"/>
+      <c r="C163" s="21"/>
+      <c r="D163" s="21"/>
+    </row>
+    <row r="164" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="21"/>
+      <c r="B164" s="21"/>
+      <c r="C164" s="21"/>
+      <c r="D164" s="21"/>
+    </row>
+    <row r="165" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="21"/>
+      <c r="B165" s="21"/>
+      <c r="C165" s="21"/>
+      <c r="D165" s="21"/>
+    </row>
+    <row r="166" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="21"/>
+      <c r="B166" s="21"/>
+      <c r="C166" s="21"/>
+      <c r="D166" s="21"/>
+    </row>
+    <row r="167" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="21"/>
+      <c r="B167" s="21"/>
+      <c r="C167" s="21"/>
+      <c r="D167" s="21"/>
+    </row>
+    <row r="168" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="21"/>
+      <c r="B168" s="21"/>
+      <c r="C168" s="21"/>
+      <c r="D168" s="21"/>
+    </row>
+    <row r="169" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="21"/>
+      <c r="B169" s="21"/>
+      <c r="C169" s="21"/>
+      <c r="D169" s="21"/>
+    </row>
+    <row r="170" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="21"/>
+      <c r="B170" s="21"/>
+      <c r="C170" s="21"/>
+      <c r="D170" s="21"/>
+    </row>
+    <row r="171" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="21"/>
+      <c r="B171" s="21"/>
+      <c r="C171" s="21"/>
+      <c r="D171" s="21"/>
+    </row>
+    <row r="172" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="21"/>
+      <c r="B172" s="21"/>
+      <c r="C172" s="21"/>
+      <c r="D172" s="21"/>
+    </row>
+    <row r="173" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="21"/>
+      <c r="B173" s="21"/>
+      <c r="C173" s="21"/>
+      <c r="D173" s="21"/>
+    </row>
+    <row r="174" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="21"/>
+      <c r="B174" s="21"/>
+      <c r="C174" s="21"/>
+      <c r="D174" s="21"/>
+    </row>
+    <row r="175" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="21"/>
+      <c r="B175" s="21"/>
+      <c r="C175" s="21"/>
+      <c r="D175" s="21"/>
+    </row>
+    <row r="176" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="21"/>
+      <c r="B176" s="21"/>
+      <c r="C176" s="21"/>
+      <c r="D176" s="21"/>
+    </row>
+    <row r="177" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="21"/>
+      <c r="B177" s="21"/>
+      <c r="C177" s="21"/>
+      <c r="D177" s="21"/>
+    </row>
+    <row r="178" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="21"/>
+      <c r="B178" s="21"/>
+      <c r="C178" s="21"/>
+      <c r="D178" s="21"/>
+    </row>
+    <row r="179" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="21"/>
+      <c r="B179" s="21"/>
+      <c r="C179" s="21"/>
+      <c r="D179" s="21"/>
+    </row>
+    <row r="180" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="21"/>
+      <c r="B180" s="21"/>
+      <c r="C180" s="21"/>
+      <c r="D180" s="21"/>
+    </row>
+    <row r="181" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="21"/>
+      <c r="B181" s="21"/>
+      <c r="C181" s="21"/>
+      <c r="D181" s="21"/>
+    </row>
+    <row r="182" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="21"/>
+      <c r="B182" s="21"/>
+      <c r="C182" s="21"/>
+      <c r="D182" s="21"/>
+    </row>
+    <row r="183" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="21"/>
+      <c r="B183" s="21"/>
+      <c r="C183" s="21"/>
+      <c r="D183" s="21"/>
+    </row>
+    <row r="184" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="21"/>
+      <c r="B184" s="21"/>
+      <c r="C184" s="21"/>
+      <c r="D184" s="21"/>
+    </row>
+    <row r="185" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="21"/>
+      <c r="B185" s="21"/>
+      <c r="C185" s="21"/>
+      <c r="D185" s="21"/>
+    </row>
+    <row r="186" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="21"/>
+      <c r="B186" s="21"/>
+      <c r="C186" s="21"/>
+      <c r="D186" s="21"/>
+    </row>
+    <row r="187" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="21"/>
+      <c r="B187" s="21"/>
+      <c r="C187" s="21"/>
+      <c r="D187" s="21"/>
+    </row>
+    <row r="188" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="21"/>
+      <c r="B188" s="21"/>
+      <c r="C188" s="21"/>
+      <c r="D188" s="21"/>
+    </row>
+    <row r="189" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="21"/>
+      <c r="B189" s="21"/>
+      <c r="C189" s="21"/>
+      <c r="D189" s="21"/>
+    </row>
+    <row r="190" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="21"/>
+      <c r="B190" s="21"/>
+      <c r="C190" s="21"/>
+      <c r="D190" s="21"/>
+    </row>
+    <row r="191" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="21"/>
+      <c r="B191" s="21"/>
+      <c r="C191" s="21"/>
+      <c r="D191" s="21"/>
+    </row>
+    <row r="192" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="21"/>
+      <c r="B192" s="21"/>
+      <c r="C192" s="21"/>
+      <c r="D192" s="21"/>
+    </row>
+    <row r="193" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="21"/>
+      <c r="B193" s="21"/>
+      <c r="C193" s="21"/>
+      <c r="D193" s="21"/>
+    </row>
+    <row r="194" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="21"/>
+      <c r="B194" s="21"/>
+      <c r="C194" s="21"/>
+      <c r="D194" s="21"/>
+    </row>
+    <row r="195" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="21"/>
+      <c r="B195" s="21"/>
+      <c r="C195" s="21"/>
+      <c r="D195" s="21"/>
+    </row>
+    <row r="196" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="21"/>
+      <c r="B196" s="21"/>
+      <c r="C196" s="21"/>
+      <c r="D196" s="21"/>
+    </row>
+    <row r="197" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="21"/>
+      <c r="B197" s="21"/>
+      <c r="C197" s="21"/>
+      <c r="D197" s="21"/>
+    </row>
+    <row r="198" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="21"/>
+      <c r="B198" s="21"/>
+      <c r="C198" s="21"/>
+      <c r="D198" s="21"/>
+    </row>
+    <row r="199" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="21"/>
+      <c r="B199" s="21"/>
+      <c r="C199" s="21"/>
+      <c r="D199" s="21"/>
+    </row>
+    <row r="200" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="21"/>
+      <c r="B200" s="21"/>
+      <c r="C200" s="21"/>
+      <c r="D200" s="21"/>
+    </row>
+    <row r="201" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="21"/>
+      <c r="B201" s="21"/>
+      <c r="C201" s="21"/>
+      <c r="D201" s="21"/>
+    </row>
+    <row r="202" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="21"/>
+      <c r="B202" s="21"/>
+      <c r="C202" s="21"/>
+      <c r="D202" s="21"/>
+    </row>
+    <row r="203" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="21"/>
+      <c r="B203" s="21"/>
+      <c r="C203" s="21"/>
+      <c r="D203" s="21"/>
+    </row>
+    <row r="204" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="21"/>
+      <c r="B204" s="21"/>
+      <c r="C204" s="21"/>
+      <c r="D204" s="21"/>
+    </row>
+    <row r="205" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="21"/>
+      <c r="B205" s="21"/>
+      <c r="C205" s="21"/>
+      <c r="D205" s="21"/>
+    </row>
+    <row r="206" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="21"/>
+      <c r="B206" s="21"/>
+      <c r="C206" s="21"/>
+      <c r="D206" s="21"/>
+    </row>
+    <row r="207" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="21"/>
+      <c r="B207" s="21"/>
+      <c r="C207" s="21"/>
+      <c r="D207" s="21"/>
+    </row>
+    <row r="208" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="21"/>
+      <c r="B208" s="21"/>
+      <c r="C208" s="21"/>
+      <c r="D208" s="21"/>
+    </row>
+    <row r="209" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="21"/>
+      <c r="B209" s="21"/>
+      <c r="C209" s="21"/>
+      <c r="D209" s="21"/>
+    </row>
+    <row r="210" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="21"/>
+      <c r="B210" s="21"/>
+      <c r="C210" s="21"/>
+      <c r="D210" s="21"/>
+    </row>
+    <row r="211" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="21"/>
+      <c r="B211" s="21"/>
+      <c r="C211" s="21"/>
+      <c r="D211" s="21"/>
+    </row>
+    <row r="212" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="21"/>
+      <c r="B212" s="21"/>
+      <c r="C212" s="21"/>
+      <c r="D212" s="21"/>
+    </row>
+    <row r="213" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="21"/>
+      <c r="B213" s="21"/>
+      <c r="C213" s="21"/>
+      <c r="D213" s="21"/>
+    </row>
+    <row r="214" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="21"/>
+      <c r="B214" s="21"/>
+      <c r="C214" s="21"/>
+      <c r="D214" s="21"/>
+    </row>
+    <row r="215" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="21"/>
+      <c r="B215" s="21"/>
+      <c r="C215" s="21"/>
+      <c r="D215" s="21"/>
+    </row>
+    <row r="216" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="21"/>
+      <c r="B216" s="21"/>
+      <c r="C216" s="21"/>
+      <c r="D216" s="21"/>
+    </row>
+    <row r="217" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="21"/>
+      <c r="B217" s="21"/>
+      <c r="C217" s="21"/>
+      <c r="D217" s="21"/>
+    </row>
+    <row r="218" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="21"/>
+      <c r="B218" s="21"/>
+      <c r="C218" s="21"/>
+      <c r="D218" s="21"/>
+    </row>
+    <row r="219" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="21"/>
+      <c r="B219" s="21"/>
+      <c r="C219" s="21"/>
+      <c r="D219" s="21"/>
+    </row>
+    <row r="220" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="21"/>
+      <c r="B220" s="21"/>
+      <c r="C220" s="21"/>
+      <c r="D220" s="21"/>
+    </row>
+    <row r="221" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="21"/>
+      <c r="B221" s="21"/>
+      <c r="C221" s="21"/>
+      <c r="D221" s="21"/>
+    </row>
+    <row r="222" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="21"/>
+      <c r="B222" s="21"/>
+      <c r="C222" s="21"/>
+      <c r="D222" s="21"/>
+    </row>
+    <row r="223" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="21"/>
+      <c r="B223" s="21"/>
+      <c r="C223" s="21"/>
+      <c r="D223" s="21"/>
+    </row>
+    <row r="224" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="21"/>
+      <c r="B224" s="21"/>
+      <c r="C224" s="21"/>
+      <c r="D224" s="21"/>
+    </row>
+    <row r="225" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="21"/>
+      <c r="B225" s="21"/>
+      <c r="C225" s="21"/>
+      <c r="D225" s="21"/>
+    </row>
+    <row r="226" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="21"/>
+      <c r="B226" s="21"/>
+      <c r="C226" s="21"/>
+      <c r="D226" s="21"/>
+    </row>
+    <row r="227" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="21"/>
+      <c r="B227" s="21"/>
+      <c r="C227" s="21"/>
+      <c r="D227" s="21"/>
+    </row>
+    <row r="228" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="21"/>
+      <c r="B228" s="21"/>
+      <c r="C228" s="21"/>
+      <c r="D228" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="N51:N58"/>
+    <mergeCell ref="R51:R58"/>
+    <mergeCell ref="N59:N63"/>
+    <mergeCell ref="R59:R63"/>
+    <mergeCell ref="N64:N68"/>
+    <mergeCell ref="R64:R68"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="N43:N47"/>
+    <mergeCell ref="R43:R47"/>
+    <mergeCell ref="N48:N49"/>
+    <mergeCell ref="R48:R49"/>
+  </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F14:F25 F30:F40" xr:uid="{67546FD1-F383-41E0-BB8B-2F4BEECE4BCF}">
+      <formula1>"Avoid,Mitigate,Accept"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="portrait"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Docs/report/TEAM_1_Project Status Report.xlsx
+++ b/Docs/report/TEAM_1_Project Status Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA-Project\QA-project-tool\Docs\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3539A87F-D063-47CA-9A59-8F5C9C2FFA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A32DD03-63C2-4072-8B8F-7CD5CAA2EBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,8 +21,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId6"/>
-    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="30" r:id="rId6"/>
+    <pivotCache cacheId="33" r:id="rId7"/>
+    <pivotCache cacheId="48" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,14 +36,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="3Ua4wsPVU2+OjJeWbmtYzx5bg+lUiDntYAmcCMaFM74="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="3Ua4wsPVU2+OjJeWbmtYzx5bg+lUiDntYAmcCMaFM74="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="144">
   <si>
     <t>Day</t>
   </si>
@@ -428,16 +429,64 @@
     <t>lack of team members due to illnes</t>
   </si>
   <si>
-    <t>backend development1</t>
+    <t>backend development</t>
   </si>
   <si>
-    <t>backend development2</t>
+    <t>front development</t>
   </si>
   <si>
-    <t>continue front development 1</t>
+    <t>global  overview</t>
   </si>
   <si>
-    <t>continue front development 2</t>
+    <t>flowcharts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">class diagram </t>
+  </si>
+  <si>
+    <t>testcase execution1</t>
+  </si>
+  <si>
+    <t>testcase execution2</t>
+  </si>
+  <si>
+    <t>testcase execution3</t>
+  </si>
+  <si>
+    <t>bug report 1</t>
+  </si>
+  <si>
+    <t>bug report 2</t>
+  </si>
+  <si>
+    <t>bug report 3</t>
+  </si>
+  <si>
+    <t>rtm 1</t>
+  </si>
+  <si>
+    <t>rtm 2</t>
+  </si>
+  <si>
+    <t>rtm 3</t>
+  </si>
+  <si>
+    <t>front - fix</t>
+  </si>
+  <si>
+    <t>backend fix</t>
+  </si>
+  <si>
+    <t>reviewing rtm</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lack of team members due to testing day </t>
+  </si>
+  <si>
+    <t>working extratime on other days</t>
   </si>
 </sst>
 </file>
@@ -881,7 +930,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1057,20 +1106,13 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1118,6 +1160,20 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1131,26 +1187,12 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2430,22 +2472,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3401,10 +3443,17 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Release#5'!$A$2:$A$7</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Release#5'!$A$2:$A$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Release#5'!$A$2:$A$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3414,24 +3463,31 @@
                 <c:pt idx="2">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Release#5'!$B$2:$B$7</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Release#5'!$B$2:$B$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Release#5'!$B$2:$B$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3460,10 +3516,17 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Release#5'!$A$2:$A$7</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Release#5'!$A$2:$A$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Release#5'!$A$2:$A$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3473,24 +3536,31 @@
                 <c:pt idx="2">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Release#5'!$C$2:$C$7</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Release#5'!$C$2:$C$7</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Release#5'!$C$2:$C$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3803,9 +3873,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Release#5'!$P$6:$P$11</c:f>
+              <c:f>'Release#5'!$P$6:$P$12</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>abdalrahman</c:v>
                 </c:pt>
@@ -3821,29 +3891,32 @@
                 <c:pt idx="4">
                   <c:v>zahraan</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>(blank)</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Release#5'!$Q$6:$Q$11</c:f>
+              <c:f>'Release#5'!$Q$6:$Q$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3871,9 +3944,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Release#5'!$P$6:$P$11</c:f>
+              <c:f>'Release#5'!$P$6:$P$12</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>abdalrahman</c:v>
                 </c:pt>
@@ -3889,29 +3962,32 @@
                 <c:pt idx="4">
                   <c:v>zahraan</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>(blank)</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Release#5'!$R$6:$R$11</c:f>
+              <c:f>'Release#5'!$R$6:$R$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>11</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4377,44 +4453,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46127.858484722223" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="29" xr:uid="{1B5D88AE-0F7B-4A50-8A6E-73B606D87387}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="I1:M30" sheet="Release#3" r:id="rId2"/>
-  </cacheSource>
-  <cacheFields count="5">
-    <cacheField name="Deliverable" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="% Completed" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Comments" numFmtId="0">
-      <sharedItems count="6">
-        <s v="nabil"/>
-        <s v="alaaa"/>
-        <s v="zahraan"/>
-        <s v="alhussin"/>
-        <s v="Boda"/>
-        <s v="abdalrahman"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Hours" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
-    </cacheField>
-    <cacheField name="Done" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46136.950225115739" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="12" xr:uid="{FD53795D-03D4-45B0-A2B6-398AA1A6D80A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46154.900077430553" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="12" xr:uid="{FD53795D-03D4-45B0-A2B6-398AA1A6D80A}">
   <cacheSource type="worksheet">
     <worksheetSource ref="I1:M13" sheet="Release#4"/>
   </cacheSource>
@@ -4449,7 +4488,170 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46154.900077662038" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="29" xr:uid="{1B5D88AE-0F7B-4A50-8A6E-73B606D87387}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="I1:M30" sheet="Release#3" r:id="rId2"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Deliverable" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="% Completed" numFmtId="9">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Comments" numFmtId="0">
+      <sharedItems count="6">
+        <s v="nabil"/>
+        <s v="alaaa"/>
+        <s v="zahraan"/>
+        <s v="alhussin"/>
+        <s v="Boda"/>
+        <s v="abdalrahman"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Hours" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
+    </cacheField>
+    <cacheField name="Done" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="10"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46154.901235763886" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="35" xr:uid="{367C2ABF-5CC9-42D0-B535-42440F190428}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="I1:M36" sheet="Release#5"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Deliverable" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="% Completed" numFmtId="9">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Comments" numFmtId="0">
+      <sharedItems containsBlank="1" count="6">
+        <s v="nabil"/>
+        <s v="zahraan"/>
+        <s v="alhussin"/>
+        <s v="abdalrahman"/>
+        <s v="alaaa"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Hours" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="4"/>
+    </cacheField>
+    <cacheField name="Done" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="4"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
+  <r>
+    <s v="sprintPlan"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="javaScript learning1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="javaScript learning2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="javaScript learning3"/>
+    <n v="1"/>
+    <x v="3"/>
+    <n v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="javaScript learning4"/>
+    <n v="1"/>
+    <x v="4"/>
+    <n v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="javaScript learning5"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="css/html learning 1"/>
+    <n v="1"/>
+    <x v="3"/>
+    <n v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="css/html learning 2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <s v="nodeJs/ExpressJS learning1"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="8"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <s v="nodeJs/ExpressJS learning2"/>
+    <n v="1"/>
+    <x v="4"/>
+    <n v="8"/>
+    <n v="8"/>
+  </r>
+  <r>
+    <s v="frontend development 1"/>
+    <n v="1"/>
+    <x v="3"/>
+    <n v="5"/>
+    <n v="5"/>
+  </r>
+  <r>
+    <s v="frontend development 2"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="5"/>
+    <n v="5"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="29">
   <r>
     <s v="sprintPlan"/>
@@ -4586,168 +4788,329 @@
   </r>
   <r>
     <s v="SRS 1"/>
+    <n v="1"/>
+    <x v="3"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="SRS 2"/>
+    <n v="1"/>
+    <x v="5"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="SRS 3"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="SRS 4"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="SRS v2 review "/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <s v="Testcase 1"/>
+    <n v="1"/>
+    <x v="3"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="Testcase 2"/>
+    <n v="1"/>
+    <x v="5"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="Testcase 3"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="Testcase 4"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="Testcase v2 review"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="4"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="35">
+  <r>
+    <s v="sprintPlan"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="backend development"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="4"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <s v="front development"/>
+    <n v="1"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <s v="global  overview"/>
+    <n v="1"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="flowcharts"/>
+    <n v="1"/>
+    <x v="3"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="class diagram "/>
+    <n v="1"/>
+    <x v="4"/>
+    <n v="2"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <s v="testcase execution1"/>
+    <n v="0"/>
+    <x v="2"/>
+    <n v="2"/>
+    <m/>
+  </r>
+  <r>
+    <s v="testcase execution2"/>
     <n v="0"/>
     <x v="3"/>
     <n v="2"/>
     <m/>
   </r>
   <r>
-    <s v="SRS 2"/>
+    <s v="testcase execution3"/>
     <n v="0"/>
-    <x v="5"/>
+    <x v="4"/>
     <n v="2"/>
     <m/>
   </r>
   <r>
-    <s v="SRS 3"/>
+    <s v="bug report 1"/>
+    <n v="0"/>
+    <x v="3"/>
+    <n v="2"/>
+    <m/>
+  </r>
+  <r>
+    <s v="bug report 2"/>
     <n v="0"/>
     <x v="2"/>
     <n v="2"/>
     <m/>
   </r>
   <r>
-    <s v="SRS 4"/>
+    <s v="bug report 3"/>
+    <n v="0"/>
+    <x v="4"/>
+    <n v="2"/>
+    <m/>
+  </r>
+  <r>
+    <s v="rtm 1"/>
+    <n v="0"/>
+    <x v="3"/>
+    <n v="4"/>
+    <m/>
+  </r>
+  <r>
+    <s v="rtm 2"/>
+    <n v="0"/>
+    <x v="2"/>
+    <n v="4"/>
+    <m/>
+  </r>
+  <r>
+    <s v="rtm 3"/>
+    <n v="0"/>
+    <x v="4"/>
+    <n v="4"/>
+    <m/>
+  </r>
+  <r>
+    <s v="front - fix"/>
     <n v="0"/>
     <x v="1"/>
     <n v="2"/>
     <m/>
   </r>
   <r>
-    <s v="SRS v2 review "/>
+    <s v="backend fix"/>
     <n v="0"/>
     <x v="0"/>
     <n v="4"/>
     <m/>
   </r>
   <r>
-    <s v="Testcase 1"/>
+    <s v="reviewing rtm"/>
     <n v="0"/>
-    <x v="3"/>
-    <n v="2"/>
+    <x v="1"/>
+    <n v="4"/>
     <m/>
   </r>
   <r>
-    <s v="Testcase 2"/>
-    <n v="0"/>
+    <m/>
+    <m/>
     <x v="5"/>
-    <n v="2"/>
+    <m/>
     <m/>
   </r>
   <r>
-    <s v="Testcase 3"/>
-    <n v="0"/>
-    <x v="1"/>
-    <n v="2"/>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
     <m/>
   </r>
   <r>
-    <s v="Testcase 4"/>
-    <n v="0"/>
-    <x v="2"/>
-    <n v="2"/>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
     <m/>
   </r>
   <r>
-    <s v="Testcase v2 review"/>
-    <n v="0"/>
-    <x v="0"/>
-    <n v="4"/>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="5"/>
+    <m/>
     <m/>
   </r>
 </pivotCacheRecords>
 </file>
 
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
-  <r>
-    <s v="sprintPlan"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <s v="javaScript learning1"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <s v="javaScript learning2"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <s v="javaScript learning3"/>
-    <n v="1"/>
-    <x v="3"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <s v="javaScript learning4"/>
-    <n v="1"/>
-    <x v="4"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <s v="javaScript learning5"/>
-    <n v="1"/>
-    <x v="0"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <s v="css/html learning 1"/>
-    <n v="1"/>
-    <x v="3"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <s v="css/html learning 2"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="3"/>
-    <n v="3"/>
-  </r>
-  <r>
-    <s v="nodeJs/ExpressJS learning1"/>
-    <n v="1"/>
-    <x v="1"/>
-    <n v="8"/>
-    <n v="8"/>
-  </r>
-  <r>
-    <s v="nodeJs/ExpressJS learning2"/>
-    <n v="1"/>
-    <x v="4"/>
-    <n v="8"/>
-    <n v="8"/>
-  </r>
-  <r>
-    <s v="frontend development 1"/>
-    <n v="1"/>
-    <x v="3"/>
-    <n v="5"/>
-    <n v="5"/>
-  </r>
-  <r>
-    <s v="frontend development 2"/>
-    <n v="1"/>
-    <x v="2"/>
-    <n v="5"/>
-    <n v="5"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AC9B1EE2-8420-4372-994D-D8DFF32FE74A}" name="Release#3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AC9B1EE2-8420-4372-994D-D8DFF32FE74A}" name="Release#3" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
   <location ref="P4:R12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField name="Deliverable" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -4855,7 +5218,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4765364D-C119-4653-A0E0-E718E239CD72}" name="Release#3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4765364D-C119-4653-A0E0-E718E239CD72}" name="Release#3" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="2">
   <location ref="P4:R11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField name="Deliverable" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -4941,18 +5304,19 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C4D24A4A-83E6-4F38-BF99-7949CBE850DD}" name="Release#3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
-  <location ref="P4:R11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5BCDE94-CE27-41A8-8811-4E3C6CFEF56E}" name="Release#3" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
+  <location ref="P4:R12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField name="Deliverable" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="% Completed" compact="0" numFmtId="9" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField name="Comments" axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" sortType="ascending">
-      <items count="6">
+      <items count="7">
+        <item x="3"/>
         <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
         <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="2"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4962,7 +5326,7 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="7">
     <i>
       <x/>
     </i>
@@ -4977,6 +5341,9 @@
     </i>
     <i>
       <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -5426,15 +5793,15 @@
       <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="95"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="87"/>
+      <c r="D12" s="87"/>
+      <c r="E12" s="87"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="88"/>
       <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5684,15 +6051,15 @@
       <c r="I26" s="10"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="95"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="88"/>
       <c r="I27" s="10"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8170,15 +8537,15 @@
       <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="95"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="87"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="88"/>
       <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8260,15 +8627,15 @@
       <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="93" t="s">
+      <c r="A21" s="86" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="94"/>
-      <c r="C21" s="94"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="95"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="88"/>
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10573,39 +10940,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="75" t="s">
+      <c r="J1" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="K1" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="75" t="s">
+      <c r="L1" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="M1" s="75" t="s">
+      <c r="M1" s="68" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66">
+      <c r="A2" s="62">
         <v>1</v>
       </c>
-      <c r="B2" s="74">
+      <c r="B2" s="67">
         <f>R43</f>
         <v>24</v>
       </c>
@@ -10613,7 +10980,7 @@
         <f>SUM(M2:M9)</f>
         <v>24</v>
       </c>
-      <c r="D2" s="73">
+      <c r="D2" s="66">
         <v>70</v>
       </c>
       <c r="I2" s="35" t="s">
@@ -10625,18 +10992,18 @@
       <c r="K2" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="72">
+      <c r="L2" s="65">
         <v>3</v>
       </c>
-      <c r="M2" s="71">
+      <c r="M2" s="64">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="62">
         <v>2</v>
       </c>
-      <c r="B3" s="65">
+      <c r="B3" s="61">
         <f>B2+R51</f>
         <v>28</v>
       </c>
@@ -10661,10 +11028,10 @@
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66">
+      <c r="A4" s="62">
         <v>3</v>
       </c>
-      <c r="B4" s="65">
+      <c r="B4" s="61">
         <f>B3+R53</f>
         <v>38</v>
       </c>
@@ -10687,17 +11054,17 @@
       <c r="M4" s="22">
         <v>3</v>
       </c>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68" t="s">
+      <c r="P4" s="70"/>
+      <c r="Q4" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="R4" s="70"/>
+      <c r="R4" s="72"/>
     </row>
     <row r="5" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="66">
+      <c r="A5" s="62">
         <v>4</v>
       </c>
-      <c r="B5" s="65">
+      <c r="B5" s="61">
         <f>B4+R54</f>
         <v>46</v>
       </c>
@@ -10720,22 +11087,22 @@
       <c r="M5" s="22">
         <v>3</v>
       </c>
-      <c r="P5" s="68" t="s">
+      <c r="P5" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="68" t="s">
+      <c r="Q5" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="R5" s="67" t="s">
+      <c r="R5" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="AB5" s="69"/>
+      <c r="AB5" s="63"/>
     </row>
     <row r="6" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66">
+      <c r="A6" s="62">
         <v>5</v>
       </c>
-      <c r="B6" s="65">
+      <c r="B6" s="61">
         <f>B5+R62</f>
         <v>58</v>
       </c>
@@ -10758,21 +11125,21 @@
       <c r="M6" s="22">
         <v>3</v>
       </c>
-      <c r="P6" s="68" t="s">
+      <c r="P6" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="Q6" s="68">
+      <c r="Q6" s="74">
         <v>9</v>
       </c>
-      <c r="R6" s="67">
-        <v>5</v>
+      <c r="R6" s="75">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="66">
+      <c r="A7" s="62">
         <v>6</v>
       </c>
-      <c r="B7" s="65">
+      <c r="B7" s="61">
         <f>B6+R67</f>
         <v>70</v>
       </c>
@@ -10795,14 +11162,14 @@
       <c r="M7" s="22">
         <v>3</v>
       </c>
-      <c r="P7" s="64" t="s">
+      <c r="P7" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="Q7" s="64">
+      <c r="Q7" s="77">
         <v>9</v>
       </c>
-      <c r="R7" s="63">
-        <v>5</v>
+      <c r="R7" s="78">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -10825,14 +11192,14 @@
       <c r="M8" s="22">
         <v>3</v>
       </c>
-      <c r="P8" s="64" t="s">
+      <c r="P8" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="Q8" s="64">
+      <c r="Q8" s="77">
         <v>11</v>
       </c>
-      <c r="R8" s="63">
-        <v>7</v>
+      <c r="R8" s="78">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -10855,13 +11222,13 @@
       <c r="M9" s="22">
         <v>3</v>
       </c>
-      <c r="P9" s="64" t="s">
+      <c r="P9" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="Q9" s="64">
+      <c r="Q9" s="77">
         <v>3</v>
       </c>
-      <c r="R9" s="63">
+      <c r="R9" s="78">
         <v>3</v>
       </c>
     </row>
@@ -10885,14 +11252,14 @@
       <c r="M10" s="22">
         <v>2</v>
       </c>
-      <c r="P10" s="64" t="s">
+      <c r="P10" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="Q10" s="64">
+      <c r="Q10" s="77">
         <v>27</v>
       </c>
-      <c r="R10" s="63">
-        <v>19</v>
+      <c r="R10" s="78">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -10915,26 +11282,26 @@
       <c r="M11" s="22">
         <v>2</v>
       </c>
-      <c r="P11" s="64" t="s">
+      <c r="P11" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="Q11" s="64">
+      <c r="Q11" s="77">
         <v>11</v>
       </c>
-      <c r="R11" s="63">
-        <v>7</v>
+      <c r="R11" s="78">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="96" t="s">
+      <c r="A12" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="97"/>
-      <c r="G12" s="97"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
       <c r="I12" s="35" t="s">
         <v>82</v>
       </c>
@@ -10950,14 +11317,14 @@
       <c r="M12" s="22">
         <v>10</v>
       </c>
-      <c r="P12" s="62" t="s">
+      <c r="P12" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="Q12" s="62">
+      <c r="Q12" s="80">
         <v>70</v>
       </c>
-      <c r="R12" s="61">
-        <v>46</v>
+      <c r="R12" s="81">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -11329,15 +11696,15 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="97"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="97"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
       <c r="I28" s="35" t="s">
         <v>66</v>
       </c>
@@ -11593,7 +11960,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="98">
+      <c r="N43" s="97">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -11607,7 +11974,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="101">
+      <c r="R43" s="92">
         <f>SUM(O43:O50)</f>
         <v>24</v>
       </c>
@@ -11617,7 +11984,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="99"/>
+      <c r="N44" s="98"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O71" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>3</v>
@@ -11629,14 +11996,14 @@
         <f t="shared" ref="Q44:Q71" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alaaa</v>
       </c>
-      <c r="R44" s="101"/>
+      <c r="R44" s="92"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="99"/>
+      <c r="N45" s="98"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -11648,14 +12015,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R45" s="101"/>
+      <c r="R45" s="92"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="99"/>
+      <c r="N46" s="98"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -11667,14 +12034,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R46" s="101"/>
+      <c r="R46" s="92"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="99"/>
+      <c r="N47" s="98"/>
       <c r="O47" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -11686,14 +12053,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R47" s="101"/>
+      <c r="R47" s="92"/>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="99"/>
+      <c r="N48" s="98"/>
       <c r="O48" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -11705,14 +12072,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R48" s="101"/>
+      <c r="R48" s="92"/>
     </row>
     <row r="49" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="99"/>
+      <c r="N49" s="98"/>
       <c r="O49" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -11724,14 +12091,14 @@
         <f t="shared" si="1"/>
         <v>Boda</v>
       </c>
-      <c r="R49" s="101"/>
+      <c r="R49" s="92"/>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
-      <c r="N50" s="100"/>
+      <c r="N50" s="99"/>
       <c r="O50" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -11743,14 +12110,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R50" s="102"/>
+      <c r="R50" s="100"/>
     </row>
     <row r="51" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="98">
+      <c r="N51" s="97">
         <v>2</v>
       </c>
       <c r="O51" s="25">
@@ -11764,7 +12131,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R51" s="103">
+      <c r="R51" s="101">
         <f>SUM(O51:O52)</f>
         <v>4</v>
       </c>
@@ -11774,7 +12141,7 @@
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="99"/>
+      <c r="N52" s="98"/>
       <c r="O52" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -11786,7 +12153,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R52" s="103"/>
+      <c r="R52" s="101"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
@@ -11817,7 +12184,7 @@
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="104">
+      <c r="N54" s="89">
         <v>4</v>
       </c>
       <c r="O54" s="25">
@@ -11831,7 +12198,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R54" s="106">
+      <c r="R54" s="91">
         <f>SUM(O54:O61)</f>
         <v>8</v>
       </c>
@@ -11841,7 +12208,7 @@
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="105"/>
+      <c r="N55" s="90"/>
       <c r="O55" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11853,14 +12220,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R55" s="101"/>
+      <c r="R55" s="92"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="105"/>
+      <c r="N56" s="90"/>
       <c r="O56" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11872,14 +12239,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R56" s="101"/>
+      <c r="R56" s="92"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="105"/>
+      <c r="N57" s="90"/>
       <c r="O57" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11891,14 +12258,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R57" s="101"/>
+      <c r="R57" s="92"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="105"/>
+      <c r="N58" s="90"/>
       <c r="O58" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11910,14 +12277,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R58" s="101"/>
+      <c r="R58" s="92"/>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="105"/>
+      <c r="N59" s="90"/>
       <c r="O59" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11929,14 +12296,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R59" s="101"/>
+      <c r="R59" s="92"/>
     </row>
     <row r="60" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="105"/>
+      <c r="N60" s="90"/>
       <c r="O60" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11948,14 +12315,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R60" s="101"/>
+      <c r="R60" s="92"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="105"/>
+      <c r="N61" s="90"/>
       <c r="O61" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -11967,14 +12334,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R61" s="107"/>
+      <c r="R61" s="93"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="104">
+      <c r="N62" s="89">
         <v>5</v>
       </c>
       <c r="O62" s="25">
@@ -11988,7 +12355,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R62" s="106">
+      <c r="R62" s="91">
         <f>SUM(O62:O66)</f>
         <v>12</v>
       </c>
@@ -11998,7 +12365,7 @@
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="105"/>
+      <c r="N63" s="90"/>
       <c r="O63" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12010,14 +12377,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R63" s="105"/>
+      <c r="R63" s="90"/>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="105"/>
+      <c r="N64" s="90"/>
       <c r="O64" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12029,14 +12396,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R64" s="105"/>
+      <c r="R64" s="90"/>
     </row>
     <row r="65" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="105"/>
+      <c r="N65" s="90"/>
       <c r="O65" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12048,14 +12415,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R65" s="105"/>
+      <c r="R65" s="90"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="108"/>
+      <c r="N66" s="94"/>
       <c r="O66" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12067,14 +12434,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R66" s="108"/>
+      <c r="R66" s="94"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="104">
+      <c r="N67" s="89">
         <v>6</v>
       </c>
       <c r="O67" s="25">
@@ -12088,7 +12455,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R67" s="106">
+      <c r="R67" s="91">
         <f>SUM(O67:O71)</f>
         <v>12</v>
       </c>
@@ -12098,7 +12465,7 @@
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="105"/>
+      <c r="N68" s="90"/>
       <c r="O68" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12110,14 +12477,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R68" s="105"/>
+      <c r="R68" s="90"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
-      <c r="N69" s="105"/>
+      <c r="N69" s="90"/>
       <c r="O69" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12129,14 +12496,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R69" s="105"/>
+      <c r="R69" s="90"/>
     </row>
     <row r="70" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="21"/>
       <c r="B70" s="21"/>
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
-      <c r="N70" s="105"/>
+      <c r="N70" s="90"/>
       <c r="O70" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12148,14 +12515,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R70" s="105"/>
+      <c r="R70" s="90"/>
     </row>
     <row r="71" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="21"/>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
-      <c r="N71" s="108"/>
+      <c r="N71" s="94"/>
       <c r="O71" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12167,7 +12534,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R71" s="108"/>
+      <c r="R71" s="94"/>
     </row>
     <row r="72" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
@@ -13139,18 +13506,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="N43:N50"/>
+    <mergeCell ref="R43:R50"/>
+    <mergeCell ref="N51:N52"/>
+    <mergeCell ref="R51:R52"/>
     <mergeCell ref="N54:N61"/>
     <mergeCell ref="R54:R61"/>
     <mergeCell ref="N62:N66"/>
     <mergeCell ref="R62:R66"/>
     <mergeCell ref="N67:N71"/>
     <mergeCell ref="R67:R71"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="N43:N50"/>
-    <mergeCell ref="R43:R50"/>
-    <mergeCell ref="N51:N52"/>
-    <mergeCell ref="R51:R52"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F14:F25 F30:F40" xr:uid="{AFC4AC33-7B9C-40BD-80E0-C1F9CEEBC5BF}">
@@ -13198,45 +13565,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="75" t="s">
+      <c r="J1" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="K1" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="75" t="s">
+      <c r="L1" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="M1" s="75" t="s">
+      <c r="M1" s="68" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66">
+      <c r="A2" s="62">
         <v>1</v>
       </c>
-      <c r="B2" s="74">
+      <c r="B2" s="67">
         <v>15</v>
       </c>
       <c r="C2" s="57">
         <v>15</v>
       </c>
-      <c r="D2" s="73">
+      <c r="D2" s="66">
         <v>50</v>
       </c>
       <c r="I2" s="35" t="s">
@@ -13248,18 +13615,18 @@
       <c r="K2" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="72">
+      <c r="L2" s="65">
         <v>3</v>
       </c>
-      <c r="M2" s="71">
+      <c r="M2" s="64">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="62">
         <v>2</v>
       </c>
-      <c r="B3" s="74">
+      <c r="B3" s="67">
         <v>15</v>
       </c>
       <c r="C3" s="57">
@@ -13283,10 +13650,10 @@
       </c>
     </row>
     <row r="4" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66">
+      <c r="A4" s="62">
         <v>3</v>
       </c>
-      <c r="B4" s="74">
+      <c r="B4" s="67">
         <v>15</v>
       </c>
       <c r="C4" s="57">
@@ -13308,17 +13675,17 @@
       <c r="M4" s="22">
         <v>3</v>
       </c>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="78" t="s">
+      <c r="P4" s="70"/>
+      <c r="Q4" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="R4" s="79"/>
+      <c r="R4" s="72"/>
     </row>
     <row r="5" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="66">
+      <c r="A5" s="62">
         <v>4</v>
       </c>
-      <c r="B5" s="74">
+      <c r="B5" s="67">
         <v>15</v>
       </c>
       <c r="C5" s="57">
@@ -13340,22 +13707,22 @@
       <c r="M5" s="22">
         <v>3</v>
       </c>
-      <c r="P5" s="78" t="s">
+      <c r="P5" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="77" t="s">
+      <c r="Q5" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="R5" s="80" t="s">
+      <c r="R5" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="AB5" s="69"/>
+      <c r="AB5" s="63"/>
     </row>
     <row r="6" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66">
+      <c r="A6" s="62">
         <v>5</v>
       </c>
-      <c r="B6" s="74">
+      <c r="B6" s="67">
         <v>15</v>
       </c>
       <c r="C6" s="57">
@@ -13377,21 +13744,21 @@
       <c r="M6" s="22">
         <v>3</v>
       </c>
-      <c r="P6" s="77" t="s">
+      <c r="P6" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="Q6" s="81">
+      <c r="Q6" s="74">
         <v>11</v>
       </c>
-      <c r="R6" s="82">
+      <c r="R6" s="75">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="66">
+      <c r="A7" s="62">
         <v>6</v>
       </c>
-      <c r="B7" s="65">
+      <c r="B7" s="61">
         <v>50</v>
       </c>
       <c r="C7" s="57">
@@ -13413,13 +13780,13 @@
       <c r="M7" s="22">
         <v>3</v>
       </c>
-      <c r="P7" s="83" t="s">
+      <c r="P7" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="Q7" s="84">
+      <c r="Q7" s="77">
         <v>11</v>
       </c>
-      <c r="R7" s="85">
+      <c r="R7" s="78">
         <v>11</v>
       </c>
     </row>
@@ -13443,13 +13810,13 @@
       <c r="M8" s="22">
         <v>3</v>
       </c>
-      <c r="P8" s="83" t="s">
+      <c r="P8" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="77">
         <v>11</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="78">
         <v>11</v>
       </c>
     </row>
@@ -13473,13 +13840,13 @@
       <c r="M9" s="22">
         <v>3</v>
       </c>
-      <c r="P9" s="83" t="s">
+      <c r="P9" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="Q9" s="84">
+      <c r="Q9" s="77">
         <v>6</v>
       </c>
-      <c r="R9" s="85">
+      <c r="R9" s="78">
         <v>6</v>
       </c>
     </row>
@@ -13503,13 +13870,13 @@
       <c r="M10" s="22">
         <v>8</v>
       </c>
-      <c r="P10" s="83" t="s">
+      <c r="P10" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="Q10" s="84">
+      <c r="Q10" s="77">
         <v>11</v>
       </c>
-      <c r="R10" s="85">
+      <c r="R10" s="78">
         <v>11</v>
       </c>
     </row>
@@ -13533,26 +13900,26 @@
       <c r="M11" s="22">
         <v>8</v>
       </c>
-      <c r="P11" s="86" t="s">
+      <c r="P11" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="Q11" s="87">
+      <c r="Q11" s="80">
         <v>50</v>
       </c>
-      <c r="R11" s="88">
+      <c r="R11" s="81">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="96" t="s">
+      <c r="A12" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="97"/>
-      <c r="G12" s="97"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
       <c r="I12" s="35" t="s">
         <v>121</v>
       </c>
@@ -13801,15 +14168,15 @@
       <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="97"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="97"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
       <c r="I28" s="35"/>
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
@@ -14033,7 +14400,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="98">
+      <c r="N43" s="97">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -14047,7 +14414,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="101">
+      <c r="R43" s="92">
         <f>SUM(O43:O47)</f>
         <v>15</v>
       </c>
@@ -14057,7 +14424,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="99"/>
+      <c r="N44" s="98"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O68" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>3</v>
@@ -14069,14 +14436,14 @@
         <f t="shared" ref="Q44:Q68" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alaaa</v>
       </c>
-      <c r="R44" s="101"/>
+      <c r="R44" s="92"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="99"/>
+      <c r="N45" s="98"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14088,14 +14455,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R45" s="101"/>
+      <c r="R45" s="92"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="99"/>
+      <c r="N46" s="98"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14107,14 +14474,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R46" s="101"/>
+      <c r="R46" s="92"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="99"/>
+      <c r="N47" s="98"/>
       <c r="O47" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14126,14 +14493,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R47" s="101"/>
+      <c r="R47" s="92"/>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="98">
+      <c r="N48" s="97">
         <v>2</v>
       </c>
       <c r="O48" s="25">
@@ -14147,7 +14514,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R48" s="103">
+      <c r="R48" s="101">
         <f>SUM(O48:O49)</f>
         <v>6</v>
       </c>
@@ -14157,7 +14524,7 @@
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="99"/>
+      <c r="N49" s="98"/>
       <c r="O49" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14169,7 +14536,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R49" s="103"/>
+      <c r="R49" s="101"/>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
@@ -14197,7 +14564,7 @@
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="104">
+      <c r="N51" s="89">
         <v>4</v>
       </c>
       <c r="O51" s="25" t="e">
@@ -14209,7 +14576,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R51" s="106">
+      <c r="R51" s="91">
         <v>0</v>
       </c>
     </row>
@@ -14218,7 +14585,7 @@
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="105"/>
+      <c r="N52" s="90"/>
       <c r="O52" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14228,14 +14595,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R52" s="101"/>
+      <c r="R52" s="92"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
-      <c r="N53" s="105"/>
+      <c r="N53" s="90"/>
       <c r="O53" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14245,14 +14612,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R53" s="101"/>
+      <c r="R53" s="92"/>
     </row>
     <row r="54" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="105"/>
+      <c r="N54" s="90"/>
       <c r="O54" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14262,14 +14629,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R54" s="101"/>
+      <c r="R54" s="92"/>
     </row>
     <row r="55" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="105"/>
+      <c r="N55" s="90"/>
       <c r="O55" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14279,14 +14646,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R55" s="101"/>
+      <c r="R55" s="92"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="105"/>
+      <c r="N56" s="90"/>
       <c r="O56" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14296,14 +14663,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R56" s="101"/>
+      <c r="R56" s="92"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="105"/>
+      <c r="N57" s="90"/>
       <c r="O57" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14313,14 +14680,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R57" s="101"/>
+      <c r="R57" s="92"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="105"/>
+      <c r="N58" s="90"/>
       <c r="O58" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14330,14 +14697,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R58" s="107"/>
+      <c r="R58" s="93"/>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="104">
+      <c r="N59" s="89">
         <v>5</v>
       </c>
       <c r="O59" s="25" t="e">
@@ -14349,7 +14716,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R59" s="106">
+      <c r="R59" s="91">
         <v>0</v>
       </c>
     </row>
@@ -14358,7 +14725,7 @@
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="105"/>
+      <c r="N60" s="90"/>
       <c r="O60" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14368,14 +14735,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R60" s="105"/>
+      <c r="R60" s="90"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="105"/>
+      <c r="N61" s="90"/>
       <c r="O61" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14385,14 +14752,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R61" s="105"/>
+      <c r="R61" s="90"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="105"/>
+      <c r="N62" s="90"/>
       <c r="O62" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14402,14 +14769,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R62" s="105"/>
+      <c r="R62" s="90"/>
     </row>
     <row r="63" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="108"/>
+      <c r="N63" s="94"/>
       <c r="O63" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14419,14 +14786,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R63" s="108"/>
+      <c r="R63" s="94"/>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="104">
+      <c r="N64" s="89">
         <v>6</v>
       </c>
       <c r="O64" s="25">
@@ -14440,7 +14807,7 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R64" s="106">
+      <c r="R64" s="91">
         <f>SUM(O64:O68)</f>
         <v>29</v>
       </c>
@@ -14450,7 +14817,7 @@
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="105"/>
+      <c r="N65" s="90"/>
       <c r="O65" s="25">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -14462,14 +14829,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R65" s="105"/>
+      <c r="R65" s="90"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="105"/>
+      <c r="N66" s="90"/>
       <c r="O66" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -14481,14 +14848,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R66" s="105"/>
+      <c r="R66" s="90"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="105"/>
+      <c r="N67" s="90"/>
       <c r="O67" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -14500,14 +14867,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R67" s="105"/>
+      <c r="R67" s="90"/>
     </row>
     <row r="68" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="108"/>
+      <c r="N68" s="94"/>
       <c r="O68" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14519,7 +14886,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R68" s="108"/>
+      <c r="R68" s="94"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
@@ -15521,7 +15888,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AB228"/>
+  <dimension ref="A1:AB227"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="25.8" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.77734375" style="20" customWidth="1"/>
@@ -15551,41 +15918,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="91" t="s">
+      <c r="C1" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="91" t="s">
+      <c r="D1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="91" t="s">
+      <c r="J1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="K1" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="91" t="s">
+      <c r="L1" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="M1" s="91" t="s">
+      <c r="M1" s="84" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66">
+      <c r="A2" s="62">
         <v>1</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="73">
+      <c r="B2" s="67">
+        <v>25</v>
+      </c>
+      <c r="C2" s="57">
+        <v>8</v>
+      </c>
+      <c r="D2" s="66">
         <v>50</v>
       </c>
       <c r="I2" s="35" t="s">
@@ -15597,63 +15968,79 @@
       <c r="K2" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="72">
-        <v>3</v>
-      </c>
-      <c r="M2" s="71"/>
+      <c r="L2" s="65">
+        <v>2</v>
+      </c>
+      <c r="M2" s="64">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="66">
+      <c r="A3" s="62">
         <v>2</v>
       </c>
-      <c r="B3" s="74"/>
-      <c r="C3" s="57"/>
+      <c r="B3" s="67">
+        <v>30</v>
+      </c>
+      <c r="C3" s="57">
+        <v>16</v>
+      </c>
       <c r="D3" s="21"/>
       <c r="I3" s="35" t="s">
         <v>124</v>
       </c>
       <c r="J3" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L3" s="22">
-        <v>8</v>
-      </c>
-      <c r="M3" s="22"/>
+        <v>4</v>
+      </c>
+      <c r="M3" s="22">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66">
+      <c r="A4" s="62">
         <v>3</v>
       </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="57"/>
+      <c r="B4" s="67">
+        <v>35</v>
+      </c>
+      <c r="C4" s="57">
+        <v>16</v>
+      </c>
       <c r="D4" s="21"/>
       <c r="I4" s="35" t="s">
         <v>125</v>
       </c>
       <c r="J4" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="L4" s="22">
-        <v>8</v>
-      </c>
-      <c r="M4" s="22"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="22">
+        <v>4</v>
+      </c>
+      <c r="P4" s="70"/>
+      <c r="Q4" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="R4" s="79"/>
+      <c r="R4" s="72"/>
     </row>
     <row r="5" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="66">
+      <c r="A5" s="62">
         <v>4</v>
       </c>
-      <c r="B5" s="74"/>
+      <c r="B5" s="67">
+        <v>40</v>
+      </c>
       <c r="C5" s="57"/>
       <c r="D5" s="21"/>
       <c r="I5" s="35" t="s">
@@ -15668,23 +16055,27 @@
       <c r="L5" s="22">
         <v>2</v>
       </c>
-      <c r="M5" s="22"/>
-      <c r="P5" s="77" t="s">
+      <c r="M5" s="22">
+        <v>2</v>
+      </c>
+      <c r="P5" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="Q5" s="77" t="s">
+      <c r="Q5" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="R5" s="80" t="s">
+      <c r="R5" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="AB5" s="69"/>
+      <c r="AB5" s="63"/>
     </row>
     <row r="6" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="66">
+      <c r="A6" s="62">
         <v>5</v>
       </c>
-      <c r="B6" s="74"/>
+      <c r="B6" s="67">
+        <v>45</v>
+      </c>
       <c r="C6" s="57"/>
       <c r="D6" s="21"/>
       <c r="I6" s="35" t="s">
@@ -15694,46 +16085,56 @@
         <v>1</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L6" s="22">
         <v>2</v>
       </c>
-      <c r="M6" s="22"/>
-      <c r="P6" s="77" t="s">
+      <c r="M6" s="22">
+        <v>2</v>
+      </c>
+      <c r="P6" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="Q6" s="81">
-        <v>11</v>
-      </c>
-      <c r="R6" s="82">
-        <v>11</v>
+      <c r="Q6" s="74">
+        <v>10</v>
+      </c>
+      <c r="R6" s="75">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="66">
+      <c r="A7" s="62">
         <v>6</v>
       </c>
-      <c r="B7" s="65"/>
+      <c r="B7" s="61">
+        <v>50</v>
+      </c>
       <c r="C7" s="57"/>
       <c r="D7" s="21"/>
-      <c r="I7" s="35"/>
+      <c r="I7" s="35" t="s">
+        <v>128</v>
+      </c>
       <c r="J7" s="43">
         <v>1</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="P7" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="Q7" s="84">
-        <v>11</v>
-      </c>
-      <c r="R7" s="85">
-        <v>11</v>
+      <c r="L7" s="22">
+        <v>2</v>
+      </c>
+      <c r="M7" s="22">
+        <v>2</v>
+      </c>
+      <c r="P7" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q7" s="77">
+        <v>10</v>
+      </c>
+      <c r="R7" s="78">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -15741,23 +16142,27 @@
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
       <c r="D8" s="21"/>
-      <c r="I8" s="35"/>
+      <c r="I8" s="35" t="s">
+        <v>129</v>
+      </c>
       <c r="J8" s="43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="L8" s="22"/>
+      <c r="L8" s="22">
+        <v>2</v>
+      </c>
       <c r="M8" s="22"/>
-      <c r="P8" s="83" t="s">
+      <c r="P8" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="Q8" s="84">
-        <v>11</v>
-      </c>
-      <c r="R8" s="85">
-        <v>11</v>
+      <c r="Q8" s="77">
+        <v>10</v>
+      </c>
+      <c r="R8" s="78">
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -15765,22 +16170,26 @@
       <c r="B9" s="21"/>
       <c r="C9" s="21"/>
       <c r="D9" s="21"/>
-      <c r="I9" s="35"/>
+      <c r="I9" s="35" t="s">
+        <v>130</v>
+      </c>
       <c r="J9" s="43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="L9" s="22"/>
+        <v>102</v>
+      </c>
+      <c r="L9" s="22">
+        <v>2</v>
+      </c>
       <c r="M9" s="22"/>
-      <c r="P9" s="83" t="s">
+      <c r="P9" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="Q9" s="84">
-        <v>6</v>
-      </c>
-      <c r="R9" s="85">
+      <c r="Q9" s="77">
+        <v>10</v>
+      </c>
+      <c r="R9" s="78">
         <v>6</v>
       </c>
     </row>
@@ -15789,23 +16198,27 @@
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
-      <c r="I10" s="35"/>
+      <c r="I10" s="35" t="s">
+        <v>131</v>
+      </c>
       <c r="J10" s="43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="22"/>
+      <c r="L10" s="22">
+        <v>2</v>
+      </c>
       <c r="M10" s="22"/>
-      <c r="P10" s="83" t="s">
+      <c r="P10" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="Q10" s="84">
-        <v>11</v>
-      </c>
-      <c r="R10" s="85">
-        <v>11</v>
+      <c r="Q10" s="77">
+        <v>10</v>
+      </c>
+      <c r="R10" s="78">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -15813,47 +16226,57 @@
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
-      <c r="I11" s="35"/>
+      <c r="I11" s="35" t="s">
+        <v>132</v>
+      </c>
       <c r="J11" s="43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="22"/>
+      <c r="L11" s="22">
+        <v>2</v>
+      </c>
       <c r="M11" s="22"/>
-      <c r="P11" s="86" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q11" s="87">
-        <v>50</v>
-      </c>
-      <c r="R11" s="88">
-        <v>50</v>
-      </c>
+      <c r="P11" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="78"/>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="96" t="s">
+      <c r="A12" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="97"/>
-      <c r="G12" s="97"/>
-      <c r="I12" s="35"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="I12" s="35" t="s">
+        <v>133</v>
+      </c>
       <c r="J12" s="43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="L12" s="22"/>
+      <c r="L12" s="22">
+        <v>2</v>
+      </c>
       <c r="M12" s="22"/>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
+      <c r="P12" s="79" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="80">
+        <v>50</v>
+      </c>
+      <c r="R12" s="81">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="55" t="s">
@@ -15877,28 +16300,40 @@
       <c r="G13" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="35"/>
+      <c r="I13" s="35" t="s">
+        <v>134</v>
+      </c>
       <c r="J13" s="43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="L13" s="22"/>
+        <v>101</v>
+      </c>
+      <c r="L13" s="22">
+        <v>2</v>
+      </c>
       <c r="M13" s="22"/>
     </row>
     <row r="14" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22"/>
-      <c r="B14" s="90"/>
+      <c r="B14" s="83"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
       <c r="F14" s="58"/>
       <c r="G14" s="37"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="22"/>
+      <c r="I14" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="J14" s="43">
+        <v>0</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="22">
+        <v>4</v>
+      </c>
       <c r="M14" s="22"/>
     </row>
     <row r="15" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -15909,10 +16344,18 @@
       <c r="E15" s="32"/>
       <c r="F15" s="57"/>
       <c r="G15" s="56"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="22"/>
+      <c r="I15" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="J15" s="43">
+        <v>0</v>
+      </c>
+      <c r="K15" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="22">
+        <v>4</v>
+      </c>
       <c r="M15" s="22"/>
     </row>
     <row r="16" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -15923,10 +16366,18 @@
       <c r="E16" s="32"/>
       <c r="F16" s="39"/>
       <c r="G16" s="29"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="22"/>
+      <c r="I16" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="43">
+        <v>0</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="L16" s="22">
+        <v>4</v>
+      </c>
       <c r="M16" s="22"/>
     </row>
     <row r="17" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -15937,10 +16388,18 @@
       <c r="E17" s="32"/>
       <c r="F17" s="41"/>
       <c r="G17" s="29"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="22"/>
+      <c r="I17" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="J17" s="43">
+        <v>0</v>
+      </c>
+      <c r="K17" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="22">
+        <v>2</v>
+      </c>
       <c r="M17" s="22"/>
     </row>
     <row r="18" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -15951,10 +16410,18 @@
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="36"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="22"/>
+      <c r="I18" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="J18" s="43">
+        <v>0</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="L18" s="22">
+        <v>4</v>
+      </c>
       <c r="M18" s="22"/>
     </row>
     <row r="19" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -15965,10 +16432,18 @@
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="22"/>
+      <c r="I19" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="J19" s="43">
+        <v>0</v>
+      </c>
+      <c r="K19" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L19" s="22">
+        <v>4</v>
+      </c>
       <c r="M19" s="22"/>
     </row>
     <row r="20" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16078,15 +16553,15 @@
       <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="96" t="s">
+      <c r="A28" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="97"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="97"/>
-      <c r="F28" s="97"/>
-      <c r="G28" s="97"/>
+      <c r="B28" s="96"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
       <c r="I28" s="35"/>
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
@@ -16126,19 +16601,21 @@
         <v>1</v>
       </c>
       <c r="B30" s="52"/>
-      <c r="C30" s="90">
+      <c r="C30" s="83">
         <v>5</v>
       </c>
       <c r="D30" s="50">
         <v>5</v>
       </c>
       <c r="E30" s="49" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="F30" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="G30" s="47"/>
+        <v>29</v>
+      </c>
+      <c r="G30" s="47" t="s">
+        <v>143</v>
+      </c>
       <c r="I30" s="35"/>
       <c r="J30" s="43"/>
       <c r="K30" s="43"/>
@@ -16244,11 +16721,11 @@
       </c>
       <c r="L37" s="22">
         <f>SUM(L2:L36)</f>
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="M37" s="22">
         <f>SUM(M2:M36)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16310,23 +16787,23 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="98">
+      <c r="N43" s="97">
         <v>1</v>
       </c>
       <c r="O43" s="25">
         <f>VLOOKUP(P43,$I$2:$L$36,4,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="P43" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="P43" s="35" t="s">
         <v>92</v>
       </c>
       <c r="Q43" s="24" t="str">
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="101" t="e">
-        <f>SUM(O43:O47)</f>
-        <v>#N/A</v>
+      <c r="R43" s="92">
+        <f>SUM(O43:O46)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16334,127 +16811,129 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="99"/>
-      <c r="O44" s="25" t="e">
-        <f t="shared" ref="O44:O68" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
-        <v>#N/A</v>
+      <c r="N44" s="98"/>
+      <c r="O44" s="25">
+        <f t="shared" ref="O44:O67" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
+        <v>2</v>
       </c>
       <c r="P44" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q44" s="24" t="e">
-        <f t="shared" ref="Q44:Q68" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="R44" s="101"/>
+        <v>126</v>
+      </c>
+      <c r="Q44" s="24" t="str">
+        <f t="shared" ref="Q44:Q67" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
+        <v>alhussin</v>
+      </c>
+      <c r="R44" s="92"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="99"/>
-      <c r="O45" s="25" t="e">
+      <c r="N45" s="98"/>
+      <c r="O45" s="25">
         <f t="shared" si="0"/>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="P45" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q45" s="24" t="e">
+        <v>127</v>
+      </c>
+      <c r="Q45" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R45" s="101"/>
+        <v>abdalrahman</v>
+      </c>
+      <c r="R45" s="92"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="99"/>
-      <c r="O46" s="25" t="e">
+      <c r="N46" s="98"/>
+      <c r="O46" s="25">
         <f t="shared" si="0"/>
-        <v>#N/A</v>
+        <v>2</v>
       </c>
       <c r="P46" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q46" s="24" t="e">
+        <v>128</v>
+      </c>
+      <c r="Q46" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R46" s="101"/>
+        <v>alaaa</v>
+      </c>
+      <c r="R46" s="92"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="25" t="e">
+      <c r="N47" s="97">
+        <v>2</v>
+      </c>
+      <c r="O47" s="25">
         <f t="shared" si="0"/>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
       <c r="P47" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q47" s="24" t="e">
+        <v>125</v>
+      </c>
+      <c r="Q47" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R47" s="101"/>
+        <v>zahraan</v>
+      </c>
+      <c r="R47" s="101">
+        <f>SUM(O47:O48)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="98">
-        <v>2</v>
-      </c>
-      <c r="O48" s="25" t="e">
+      <c r="N48" s="98"/>
+      <c r="O48" s="25">
         <f t="shared" si="0"/>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
       <c r="P48" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q48" s="28" t="e">
+        <v>124</v>
+      </c>
+      <c r="Q48" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R48" s="103" t="e">
-        <f>SUM(O48:O49)</f>
-        <v>#N/A</v>
-      </c>
+        <v>nabil</v>
+      </c>
+      <c r="R48" s="101"/>
     </row>
     <row r="49" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="99"/>
+      <c r="N49" s="85">
+        <v>3</v>
+      </c>
       <c r="O49" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="P49" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q49" s="28" t="e">
+      <c r="P49" s="24"/>
+      <c r="Q49" s="24" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R49" s="103"/>
+      <c r="R49" s="82">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
-      <c r="N50" s="92">
-        <v>3</v>
+      <c r="N50" s="89">
+        <v>4</v>
       </c>
       <c r="O50" s="25" t="e">
         <f t="shared" si="0"/>
@@ -16465,7 +16944,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R50" s="89">
+      <c r="R50" s="91">
         <v>0</v>
       </c>
     </row>
@@ -16474,9 +16953,7 @@
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="104">
-        <v>4</v>
-      </c>
+      <c r="N51" s="90"/>
       <c r="O51" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16486,16 +16963,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R51" s="106">
-        <v>0</v>
-      </c>
+      <c r="R51" s="92"/>
     </row>
     <row r="52" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="21"/>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="105"/>
+      <c r="N52" s="90"/>
       <c r="O52" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16505,14 +16980,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R52" s="101"/>
+      <c r="R52" s="92"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
-      <c r="N53" s="105"/>
+      <c r="N53" s="90"/>
       <c r="O53" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16522,14 +16997,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R53" s="101"/>
+      <c r="R53" s="92"/>
     </row>
     <row r="54" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="105"/>
+      <c r="N54" s="90"/>
       <c r="O54" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16539,14 +17014,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R54" s="101"/>
+      <c r="R54" s="92"/>
     </row>
     <row r="55" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="105"/>
+      <c r="N55" s="90"/>
       <c r="O55" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16556,14 +17031,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R55" s="101"/>
+      <c r="R55" s="92"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="105"/>
+      <c r="N56" s="90"/>
       <c r="O56" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16573,14 +17048,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R56" s="101"/>
+      <c r="R56" s="92"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="105"/>
+      <c r="N57" s="90"/>
       <c r="O57" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16590,14 +17065,16 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R57" s="101"/>
+      <c r="R57" s="93"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="105"/>
+      <c r="N58" s="89">
+        <v>5</v>
+      </c>
       <c r="O58" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16607,16 +17084,16 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R58" s="107"/>
+      <c r="R58" s="91">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="104">
-        <v>5</v>
-      </c>
+      <c r="N59" s="90"/>
       <c r="O59" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16626,16 +17103,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R59" s="106">
-        <v>0</v>
-      </c>
+      <c r="R59" s="90"/>
     </row>
     <row r="60" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="105"/>
+      <c r="N60" s="90"/>
       <c r="O60" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16645,14 +17120,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R60" s="105"/>
+      <c r="R60" s="90"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="105"/>
+      <c r="N61" s="90"/>
       <c r="O61" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16662,14 +17137,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R61" s="105"/>
+      <c r="R61" s="90"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="105"/>
+      <c r="N62" s="94"/>
       <c r="O62" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16679,138 +17154,117 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R62" s="105"/>
+      <c r="R62" s="94"/>
     </row>
     <row r="63" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="108"/>
+      <c r="N63" s="89">
+        <v>6</v>
+      </c>
       <c r="O63" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="P63" s="24"/>
+      <c r="P63" s="35"/>
       <c r="Q63" s="24" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R63" s="108"/>
+      <c r="R63" s="91" t="e">
+        <f>SUM(O63:O67)</f>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="104">
-        <v>6</v>
-      </c>
+      <c r="N64" s="90"/>
       <c r="O64" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="P64" s="35" t="s">
-        <v>119</v>
-      </c>
+      <c r="P64" s="35"/>
       <c r="Q64" s="24" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R64" s="106" t="e">
-        <f>SUM(O64:O68)</f>
-        <v>#N/A</v>
-      </c>
+      <c r="R64" s="90"/>
     </row>
     <row r="65" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="105"/>
+      <c r="N65" s="90"/>
       <c r="O65" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="P65" s="35" t="s">
-        <v>120</v>
-      </c>
+      <c r="P65" s="35"/>
       <c r="Q65" s="24" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R65" s="105"/>
+      <c r="R65" s="90"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="105"/>
+      <c r="N66" s="90"/>
       <c r="O66" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="P66" s="35" t="s">
-        <v>121</v>
-      </c>
+      <c r="P66" s="35"/>
       <c r="Q66" s="24" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R66" s="105"/>
+      <c r="R66" s="90"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="105"/>
+      <c r="N67" s="94"/>
       <c r="O67" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-      <c r="P67" s="35" t="s">
-        <v>122</v>
-      </c>
+      <c r="P67" s="35"/>
       <c r="Q67" s="24" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R67" s="105"/>
+      <c r="R67" s="94"/>
     </row>
     <row r="68" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="108"/>
-      <c r="O68" s="25" t="e">
-        <f t="shared" si="0"/>
+      <c r="P68" s="24"/>
+      <c r="Q68" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="R68" s="22" t="e">
+        <f>SUM(R43:R67)</f>
         <v>#N/A</v>
       </c>
-      <c r="P68" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q68" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R68" s="108"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
-      <c r="P69" s="24"/>
-      <c r="Q69" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="R69" s="22" t="e">
-        <f>SUM(R43:R68)</f>
-        <v>#N/A</v>
-      </c>
     </row>
     <row r="70" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="21"/>
@@ -17760,26 +18214,20 @@
       <c r="C227" s="21"/>
       <c r="D227" s="21"/>
     </row>
-    <row r="228" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="21"/>
-      <c r="B228" s="21"/>
-      <c r="C228" s="21"/>
-      <c r="D228" s="21"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="N51:N58"/>
-    <mergeCell ref="R51:R58"/>
-    <mergeCell ref="N59:N63"/>
-    <mergeCell ref="R59:R63"/>
-    <mergeCell ref="N64:N68"/>
-    <mergeCell ref="R64:R68"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="N43:N47"/>
-    <mergeCell ref="R43:R47"/>
-    <mergeCell ref="N48:N49"/>
-    <mergeCell ref="R48:R49"/>
+    <mergeCell ref="N43:N46"/>
+    <mergeCell ref="R43:R46"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="N50:N57"/>
+    <mergeCell ref="R50:R57"/>
+    <mergeCell ref="N58:N62"/>
+    <mergeCell ref="R58:R62"/>
+    <mergeCell ref="N63:N67"/>
+    <mergeCell ref="R63:R67"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <dataValidations count="1">

--- a/Docs/report/TEAM_1_Project Status Report.xlsx
+++ b/Docs/report/TEAM_1_Project Status Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA-Project\QA-project-tool\Docs\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A32DD03-63C2-4072-8B8F-7CD5CAA2EBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F521E447-E0AF-4F23-B26E-C462D08B54C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,9 +21,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="30" r:id="rId6"/>
-    <pivotCache cacheId="33" r:id="rId7"/>
-    <pivotCache cacheId="48" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
+    <pivotCache cacheId="2" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="146">
   <si>
     <t>Day</t>
   </si>
@@ -487,6 +487,12 @@
   </si>
   <si>
     <t>working extratime on other days</t>
+  </si>
+  <si>
+    <t>exploratory session 1</t>
+  </si>
+  <si>
+    <t>exploratory session 2</t>
   </si>
 </sst>
 </file>
@@ -1160,20 +1166,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1187,12 +1179,26 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5110,7 +5116,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AC9B1EE2-8420-4372-994D-D8DFF32FE74A}" name="Release#3" cacheId="33" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AC9B1EE2-8420-4372-994D-D8DFF32FE74A}" name="Release#3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
   <location ref="P4:R12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField name="Deliverable" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -5218,7 +5224,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4765364D-C119-4653-A0E0-E718E239CD72}" name="Release#3" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4765364D-C119-4653-A0E0-E718E239CD72}" name="Release#3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="2">
   <location ref="P4:R11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField name="Deliverable" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -5304,7 +5310,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5BCDE94-CE27-41A8-8811-4E3C6CFEF56E}" name="Release#3" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5BCDE94-CE27-41A8-8811-4E3C6CFEF56E}" name="Release#3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
   <location ref="P4:R12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField name="Deliverable" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -11293,15 +11299,15 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
       <c r="I12" s="35" t="s">
         <v>82</v>
       </c>
@@ -11696,15 +11702,15 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="95" t="s">
+      <c r="A28" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="96"/>
-      <c r="F28" s="96"/>
-      <c r="G28" s="96"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
       <c r="I28" s="35" t="s">
         <v>66</v>
       </c>
@@ -11960,7 +11966,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="97">
+      <c r="N43" s="91">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -11974,7 +11980,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="92">
+      <c r="R43" s="94">
         <f>SUM(O43:O50)</f>
         <v>24</v>
       </c>
@@ -11984,7 +11990,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="98"/>
+      <c r="N44" s="92"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O71" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>3</v>
@@ -11996,14 +12002,14 @@
         <f t="shared" ref="Q44:Q71" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alaaa</v>
       </c>
-      <c r="R44" s="92"/>
+      <c r="R44" s="94"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="98"/>
+      <c r="N45" s="92"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12015,14 +12021,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R45" s="92"/>
+      <c r="R45" s="94"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="98"/>
+      <c r="N46" s="92"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12034,14 +12040,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R46" s="92"/>
+      <c r="R46" s="94"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="98"/>
+      <c r="N47" s="92"/>
       <c r="O47" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12053,14 +12059,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R47" s="92"/>
+      <c r="R47" s="94"/>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="98"/>
+      <c r="N48" s="92"/>
       <c r="O48" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12072,14 +12078,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R48" s="92"/>
+      <c r="R48" s="94"/>
     </row>
     <row r="49" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="98"/>
+      <c r="N49" s="92"/>
       <c r="O49" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12091,14 +12097,14 @@
         <f t="shared" si="1"/>
         <v>Boda</v>
       </c>
-      <c r="R49" s="92"/>
+      <c r="R49" s="94"/>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
-      <c r="N50" s="99"/>
+      <c r="N50" s="93"/>
       <c r="O50" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12110,14 +12116,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R50" s="100"/>
+      <c r="R50" s="95"/>
     </row>
     <row r="51" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="97">
+      <c r="N51" s="91">
         <v>2</v>
       </c>
       <c r="O51" s="25">
@@ -12131,7 +12137,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R51" s="101">
+      <c r="R51" s="96">
         <f>SUM(O51:O52)</f>
         <v>4</v>
       </c>
@@ -12141,7 +12147,7 @@
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="98"/>
+      <c r="N52" s="92"/>
       <c r="O52" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12153,7 +12159,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R52" s="101"/>
+      <c r="R52" s="96"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
@@ -12184,7 +12190,7 @@
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="89">
+      <c r="N54" s="97">
         <v>4</v>
       </c>
       <c r="O54" s="25">
@@ -12198,7 +12204,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R54" s="91">
+      <c r="R54" s="99">
         <f>SUM(O54:O61)</f>
         <v>8</v>
       </c>
@@ -12208,7 +12214,7 @@
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="90"/>
+      <c r="N55" s="98"/>
       <c r="O55" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12220,14 +12226,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R55" s="92"/>
+      <c r="R55" s="94"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="90"/>
+      <c r="N56" s="98"/>
       <c r="O56" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12239,14 +12245,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R56" s="92"/>
+      <c r="R56" s="94"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="90"/>
+      <c r="N57" s="98"/>
       <c r="O57" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12258,14 +12264,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R57" s="92"/>
+      <c r="R57" s="94"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="90"/>
+      <c r="N58" s="98"/>
       <c r="O58" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12277,14 +12283,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R58" s="92"/>
+      <c r="R58" s="94"/>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="90"/>
+      <c r="N59" s="98"/>
       <c r="O59" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12296,14 +12302,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R59" s="92"/>
+      <c r="R59" s="94"/>
     </row>
     <row r="60" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="90"/>
+      <c r="N60" s="98"/>
       <c r="O60" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12315,14 +12321,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R60" s="92"/>
+      <c r="R60" s="94"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="90"/>
+      <c r="N61" s="98"/>
       <c r="O61" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12334,14 +12340,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R61" s="93"/>
+      <c r="R61" s="100"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="89">
+      <c r="N62" s="97">
         <v>5</v>
       </c>
       <c r="O62" s="25">
@@ -12355,7 +12361,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R62" s="91">
+      <c r="R62" s="99">
         <f>SUM(O62:O66)</f>
         <v>12</v>
       </c>
@@ -12365,7 +12371,7 @@
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="90"/>
+      <c r="N63" s="98"/>
       <c r="O63" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12377,14 +12383,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R63" s="90"/>
+      <c r="R63" s="98"/>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="90"/>
+      <c r="N64" s="98"/>
       <c r="O64" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12396,14 +12402,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R64" s="90"/>
+      <c r="R64" s="98"/>
     </row>
     <row r="65" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="90"/>
+      <c r="N65" s="98"/>
       <c r="O65" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12415,14 +12421,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R65" s="90"/>
+      <c r="R65" s="98"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="94"/>
+      <c r="N66" s="101"/>
       <c r="O66" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12434,14 +12440,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R66" s="94"/>
+      <c r="R66" s="101"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="89">
+      <c r="N67" s="97">
         <v>6</v>
       </c>
       <c r="O67" s="25">
@@ -12455,7 +12461,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R67" s="91">
+      <c r="R67" s="99">
         <f>SUM(O67:O71)</f>
         <v>12</v>
       </c>
@@ -12465,7 +12471,7 @@
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="90"/>
+      <c r="N68" s="98"/>
       <c r="O68" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12477,14 +12483,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R68" s="90"/>
+      <c r="R68" s="98"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
-      <c r="N69" s="90"/>
+      <c r="N69" s="98"/>
       <c r="O69" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12496,14 +12502,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R69" s="90"/>
+      <c r="R69" s="98"/>
     </row>
     <row r="70" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="21"/>
       <c r="B70" s="21"/>
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
-      <c r="N70" s="90"/>
+      <c r="N70" s="98"/>
       <c r="O70" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12515,14 +12521,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R70" s="90"/>
+      <c r="R70" s="98"/>
     </row>
     <row r="71" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="21"/>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
-      <c r="N71" s="94"/>
+      <c r="N71" s="101"/>
       <c r="O71" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12534,7 +12540,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R71" s="94"/>
+      <c r="R71" s="101"/>
     </row>
     <row r="72" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
@@ -13506,18 +13512,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N54:N61"/>
+    <mergeCell ref="R54:R61"/>
+    <mergeCell ref="N62:N66"/>
+    <mergeCell ref="R62:R66"/>
+    <mergeCell ref="N67:N71"/>
+    <mergeCell ref="R67:R71"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="N43:N50"/>
     <mergeCell ref="R43:R50"/>
     <mergeCell ref="N51:N52"/>
     <mergeCell ref="R51:R52"/>
-    <mergeCell ref="N54:N61"/>
-    <mergeCell ref="R54:R61"/>
-    <mergeCell ref="N62:N66"/>
-    <mergeCell ref="R62:R66"/>
-    <mergeCell ref="N67:N71"/>
-    <mergeCell ref="R67:R71"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F14:F25 F30:F40" xr:uid="{AFC4AC33-7B9C-40BD-80E0-C1F9CEEBC5BF}">
@@ -13911,15 +13917,15 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
       <c r="I12" s="35" t="s">
         <v>121</v>
       </c>
@@ -14168,15 +14174,15 @@
       <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="95" t="s">
+      <c r="A28" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="96"/>
-      <c r="F28" s="96"/>
-      <c r="G28" s="96"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
       <c r="I28" s="35"/>
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
@@ -14400,7 +14406,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="97">
+      <c r="N43" s="91">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -14414,7 +14420,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="92">
+      <c r="R43" s="94">
         <f>SUM(O43:O47)</f>
         <v>15</v>
       </c>
@@ -14424,7 +14430,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="98"/>
+      <c r="N44" s="92"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O68" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>3</v>
@@ -14436,14 +14442,14 @@
         <f t="shared" ref="Q44:Q68" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alaaa</v>
       </c>
-      <c r="R44" s="92"/>
+      <c r="R44" s="94"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="98"/>
+      <c r="N45" s="92"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14455,14 +14461,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R45" s="92"/>
+      <c r="R45" s="94"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="98"/>
+      <c r="N46" s="92"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14474,14 +14480,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R46" s="92"/>
+      <c r="R46" s="94"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="98"/>
+      <c r="N47" s="92"/>
       <c r="O47" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14493,14 +14499,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R47" s="92"/>
+      <c r="R47" s="94"/>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="97">
+      <c r="N48" s="91">
         <v>2</v>
       </c>
       <c r="O48" s="25">
@@ -14514,7 +14520,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R48" s="101">
+      <c r="R48" s="96">
         <f>SUM(O48:O49)</f>
         <v>6</v>
       </c>
@@ -14524,7 +14530,7 @@
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="98"/>
+      <c r="N49" s="92"/>
       <c r="O49" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14536,7 +14542,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R49" s="101"/>
+      <c r="R49" s="96"/>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
@@ -14564,7 +14570,7 @@
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="89">
+      <c r="N51" s="97">
         <v>4</v>
       </c>
       <c r="O51" s="25" t="e">
@@ -14576,7 +14582,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R51" s="91">
+      <c r="R51" s="99">
         <v>0</v>
       </c>
     </row>
@@ -14585,7 +14591,7 @@
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="90"/>
+      <c r="N52" s="98"/>
       <c r="O52" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14595,14 +14601,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R52" s="92"/>
+      <c r="R52" s="94"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
-      <c r="N53" s="90"/>
+      <c r="N53" s="98"/>
       <c r="O53" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14612,14 +14618,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R53" s="92"/>
+      <c r="R53" s="94"/>
     </row>
     <row r="54" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="90"/>
+      <c r="N54" s="98"/>
       <c r="O54" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14629,14 +14635,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R54" s="92"/>
+      <c r="R54" s="94"/>
     </row>
     <row r="55" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="90"/>
+      <c r="N55" s="98"/>
       <c r="O55" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14646,14 +14652,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R55" s="92"/>
+      <c r="R55" s="94"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="90"/>
+      <c r="N56" s="98"/>
       <c r="O56" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14663,14 +14669,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R56" s="92"/>
+      <c r="R56" s="94"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="90"/>
+      <c r="N57" s="98"/>
       <c r="O57" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14680,14 +14686,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R57" s="92"/>
+      <c r="R57" s="94"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="90"/>
+      <c r="N58" s="98"/>
       <c r="O58" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14697,14 +14703,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R58" s="93"/>
+      <c r="R58" s="100"/>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="89">
+      <c r="N59" s="97">
         <v>5</v>
       </c>
       <c r="O59" s="25" t="e">
@@ -14716,7 +14722,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R59" s="91">
+      <c r="R59" s="99">
         <v>0</v>
       </c>
     </row>
@@ -14725,7 +14731,7 @@
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="90"/>
+      <c r="N60" s="98"/>
       <c r="O60" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14735,14 +14741,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R60" s="90"/>
+      <c r="R60" s="98"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="90"/>
+      <c r="N61" s="98"/>
       <c r="O61" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14752,14 +14758,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R61" s="90"/>
+      <c r="R61" s="98"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="90"/>
+      <c r="N62" s="98"/>
       <c r="O62" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14769,14 +14775,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R62" s="90"/>
+      <c r="R62" s="98"/>
     </row>
     <row r="63" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="94"/>
+      <c r="N63" s="101"/>
       <c r="O63" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14786,14 +14792,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R63" s="94"/>
+      <c r="R63" s="101"/>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="89">
+      <c r="N64" s="97">
         <v>6</v>
       </c>
       <c r="O64" s="25">
@@ -14807,7 +14813,7 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R64" s="91">
+      <c r="R64" s="99">
         <f>SUM(O64:O68)</f>
         <v>29</v>
       </c>
@@ -14817,7 +14823,7 @@
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="90"/>
+      <c r="N65" s="98"/>
       <c r="O65" s="25">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -14829,14 +14835,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R65" s="90"/>
+      <c r="R65" s="98"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="90"/>
+      <c r="N66" s="98"/>
       <c r="O66" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -14848,14 +14854,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R66" s="90"/>
+      <c r="R66" s="98"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="90"/>
+      <c r="N67" s="98"/>
       <c r="O67" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -14867,14 +14873,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R67" s="90"/>
+      <c r="R67" s="98"/>
     </row>
     <row r="68" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="94"/>
+      <c r="N68" s="101"/>
       <c r="O68" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14886,7 +14892,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R68" s="94"/>
+      <c r="R68" s="101"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
@@ -16246,15 +16252,15 @@
       <c r="R11" s="78"/>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="95" t="s">
+      <c r="A12" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
       <c r="I12" s="35" t="s">
         <v>133</v>
       </c>
@@ -16420,7 +16426,7 @@
         <v>97</v>
       </c>
       <c r="L18" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M18" s="22"/>
     </row>
@@ -16442,7 +16448,7 @@
         <v>100</v>
       </c>
       <c r="L19" s="22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M19" s="22"/>
     </row>
@@ -16454,10 +16460,18 @@
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="22"/>
+      <c r="I20" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="J20" s="43">
+        <v>0</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" s="22">
+        <v>1</v>
+      </c>
       <c r="M20" s="22"/>
     </row>
     <row r="21" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16468,10 +16482,18 @@
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="22"/>
+      <c r="I21" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" s="43">
+        <v>0</v>
+      </c>
+      <c r="K21" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="L21" s="22">
+        <v>1</v>
+      </c>
       <c r="M21" s="22"/>
     </row>
     <row r="22" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16553,15 +16575,15 @@
       <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="95" t="s">
+      <c r="A28" s="89" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="96"/>
-      <c r="F28" s="96"/>
-      <c r="G28" s="96"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
       <c r="I28" s="35"/>
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
@@ -16787,7 +16809,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="97">
+      <c r="N43" s="91">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -16801,7 +16823,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="92">
+      <c r="R43" s="94">
         <f>SUM(O43:O46)</f>
         <v>8</v>
       </c>
@@ -16811,7 +16833,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="98"/>
+      <c r="N44" s="92"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O67" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>2</v>
@@ -16823,14 +16845,14 @@
         <f t="shared" ref="Q44:Q67" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alhussin</v>
       </c>
-      <c r="R44" s="92"/>
+      <c r="R44" s="94"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="98"/>
+      <c r="N45" s="92"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -16842,14 +16864,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R45" s="92"/>
+      <c r="R45" s="94"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="98"/>
+      <c r="N46" s="92"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -16861,14 +16883,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R46" s="92"/>
+      <c r="R46" s="94"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="97">
+      <c r="N47" s="91">
         <v>2</v>
       </c>
       <c r="O47" s="25">
@@ -16882,7 +16904,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R47" s="101">
+      <c r="R47" s="96">
         <f>SUM(O47:O48)</f>
         <v>8</v>
       </c>
@@ -16892,7 +16914,7 @@
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="98"/>
+      <c r="N48" s="92"/>
       <c r="O48" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -16904,7 +16926,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R48" s="101"/>
+      <c r="R48" s="96"/>
     </row>
     <row r="49" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
@@ -16932,7 +16954,7 @@
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
-      <c r="N50" s="89">
+      <c r="N50" s="97">
         <v>4</v>
       </c>
       <c r="O50" s="25" t="e">
@@ -16944,7 +16966,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R50" s="91">
+      <c r="R50" s="99">
         <v>0</v>
       </c>
     </row>
@@ -16953,7 +16975,7 @@
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="90"/>
+      <c r="N51" s="98"/>
       <c r="O51" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16963,14 +16985,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R51" s="92"/>
+      <c r="R51" s="94"/>
     </row>
     <row r="52" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="21"/>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="90"/>
+      <c r="N52" s="98"/>
       <c r="O52" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16980,14 +17002,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R52" s="92"/>
+      <c r="R52" s="94"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
-      <c r="N53" s="90"/>
+      <c r="N53" s="98"/>
       <c r="O53" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -16997,14 +17019,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R53" s="92"/>
+      <c r="R53" s="94"/>
     </row>
     <row r="54" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="90"/>
+      <c r="N54" s="98"/>
       <c r="O54" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17014,14 +17036,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R54" s="92"/>
+      <c r="R54" s="94"/>
     </row>
     <row r="55" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="90"/>
+      <c r="N55" s="98"/>
       <c r="O55" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17031,14 +17053,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R55" s="92"/>
+      <c r="R55" s="94"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="90"/>
+      <c r="N56" s="98"/>
       <c r="O56" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17048,14 +17070,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R56" s="92"/>
+      <c r="R56" s="94"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="90"/>
+      <c r="N57" s="98"/>
       <c r="O57" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17065,14 +17087,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R57" s="93"/>
+      <c r="R57" s="100"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="89">
+      <c r="N58" s="97">
         <v>5</v>
       </c>
       <c r="O58" s="25" t="e">
@@ -17084,7 +17106,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R58" s="91">
+      <c r="R58" s="99">
         <v>0</v>
       </c>
     </row>
@@ -17093,7 +17115,7 @@
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="90"/>
+      <c r="N59" s="98"/>
       <c r="O59" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17103,14 +17125,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R59" s="90"/>
+      <c r="R59" s="98"/>
     </row>
     <row r="60" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="90"/>
+      <c r="N60" s="98"/>
       <c r="O60" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17120,14 +17142,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R60" s="90"/>
+      <c r="R60" s="98"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="90"/>
+      <c r="N61" s="98"/>
       <c r="O61" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17137,14 +17159,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R61" s="90"/>
+      <c r="R61" s="98"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="94"/>
+      <c r="N62" s="101"/>
       <c r="O62" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17154,14 +17176,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R62" s="94"/>
+      <c r="R62" s="101"/>
     </row>
     <row r="63" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="89">
+      <c r="N63" s="97">
         <v>6</v>
       </c>
       <c r="O63" s="25" t="e">
@@ -17173,7 +17195,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R63" s="91" t="e">
+      <c r="R63" s="99" t="e">
         <f>SUM(O63:O67)</f>
         <v>#N/A</v>
       </c>
@@ -17183,7 +17205,7 @@
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="90"/>
+      <c r="N64" s="98"/>
       <c r="O64" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17193,14 +17215,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R64" s="90"/>
+      <c r="R64" s="98"/>
     </row>
     <row r="65" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="90"/>
+      <c r="N65" s="98"/>
       <c r="O65" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17210,14 +17232,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R65" s="90"/>
+      <c r="R65" s="98"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="90"/>
+      <c r="N66" s="98"/>
       <c r="O66" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17227,14 +17249,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R66" s="90"/>
+      <c r="R66" s="98"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="94"/>
+      <c r="N67" s="101"/>
       <c r="O67" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -17244,7 +17266,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R67" s="94"/>
+      <c r="R67" s="101"/>
     </row>
     <row r="68" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
@@ -18216,18 +18238,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="N50:N57"/>
+    <mergeCell ref="R50:R57"/>
+    <mergeCell ref="N58:N62"/>
+    <mergeCell ref="R58:R62"/>
+    <mergeCell ref="N63:N67"/>
+    <mergeCell ref="R63:R67"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="N43:N46"/>
     <mergeCell ref="R43:R46"/>
     <mergeCell ref="N47:N48"/>
     <mergeCell ref="R47:R48"/>
-    <mergeCell ref="N50:N57"/>
-    <mergeCell ref="R50:R57"/>
-    <mergeCell ref="N58:N62"/>
-    <mergeCell ref="R58:R62"/>
-    <mergeCell ref="N63:N67"/>
-    <mergeCell ref="R63:R67"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <dataValidations count="1">

--- a/Docs/report/TEAM_1_Project Status Report.xlsx
+++ b/Docs/report/TEAM_1_Project Status Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA-Project\QA-project-tool\Docs\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F521E447-E0AF-4F23-B26E-C462D08B54C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAF77E4-6BBE-42E8-A9BA-1AEA1216D026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId6"/>
     <pivotCache cacheId="1" r:id="rId7"/>
-    <pivotCache cacheId="2" r:id="rId8"/>
+    <pivotCache cacheId="5" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -4532,7 +4532,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46154.901235763886" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="35" xr:uid="{367C2ABF-5CC9-42D0-B535-42440F190428}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46154.907096064817" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="35" xr:uid="{367C2ABF-5CC9-42D0-B535-42440F190428}">
   <cacheSource type="worksheet">
     <worksheetSource ref="I1:M36" sheet="Release#5"/>
   </cacheSource>
@@ -4554,7 +4554,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Hours" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="4"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="4"/>
     </cacheField>
     <cacheField name="Done" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="4"/>
@@ -4983,28 +4983,28 @@
     <s v="backend fix"/>
     <n v="0"/>
     <x v="0"/>
-    <n v="4"/>
+    <n v="3"/>
     <m/>
   </r>
   <r>
     <s v="reviewing rtm"/>
     <n v="0"/>
     <x v="1"/>
-    <n v="4"/>
+    <n v="3"/>
     <m/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <x v="5"/>
-    <m/>
+    <s v="exploratory session 1"/>
+    <n v="0"/>
+    <x v="1"/>
+    <n v="1"/>
     <m/>
   </r>
   <r>
-    <m/>
-    <m/>
-    <x v="5"/>
-    <m/>
+    <s v="exploratory session 2"/>
+    <n v="0"/>
+    <x v="0"/>
+    <n v="1"/>
     <m/>
   </r>
   <r>
@@ -5310,7 +5310,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5BCDE94-CE27-41A8-8811-4E3C6CFEF56E}" name="Release#3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5BCDE94-CE27-41A8-8811-4E3C6CFEF56E}" name="Release#3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="7" compact="0" compactData="0" chartFormat="3">
   <location ref="P4:R12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField name="Deliverable" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>

--- a/Docs/report/TEAM_1_Project Status Report.xlsx
+++ b/Docs/report/TEAM_1_Project Status Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\QA-Project\QA-project-tool\Docs\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAF77E4-6BBE-42E8-A9BA-1AEA1216D026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1ABC05-16D9-4490-85DA-A714A932143F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="146">
   <si>
     <t>Day</t>
   </si>
@@ -936,7 +936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1149,23 +1149,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1179,26 +1187,13 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3449,17 +3444,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Release#5'!$A$2:$A$7</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Release#5'!$A$2:$A$4</c:f>
+              <c:f>'Release#5'!$A$2:$A$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3468,23 +3456,25 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Release#5'!$B$2:$B$7</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Release#5'!$B$2:$B$4</c:f>
+              <c:f>'Release#5'!$B$2:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>25</c:v>
                 </c:pt>
@@ -3493,6 +3483,15 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3522,17 +3521,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Release#5'!$A$2:$A$7</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Release#5'!$A$2:$A$4</c:f>
+              <c:f>'Release#5'!$A$2:$A$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3541,23 +3533,25 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                  <c15:fullRef>
-                    <c15:sqref>'Release#5'!$C$2:$C$7</c15:sqref>
-                  </c15:fullRef>
-                </c:ext>
-              </c:extLst>
-              <c:f>'Release#5'!$C$2:$C$4</c:f>
+              <c:f>'Release#5'!$C$2:$C$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>8</c:v>
                 </c:pt>
@@ -3566,6 +3560,15 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3981,19 +3984,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4532,7 +4535,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46154.907096064817" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="35" xr:uid="{367C2ABF-5CC9-42D0-B535-42440F190428}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="NV" refreshedDate="46157.909595949073" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="35" xr:uid="{367C2ABF-5CC9-42D0-B535-42440F190428}">
   <cacheSource type="worksheet">
     <worksheetSource ref="I1:M36" sheet="Release#5"/>
   </cacheSource>
@@ -4541,7 +4544,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="% Completed" numFmtId="9">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
     <cacheField name="Comments" numFmtId="0">
       <sharedItems containsBlank="1" count="6">
@@ -4557,7 +4560,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="4"/>
     </cacheField>
     <cacheField name="Done" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="4"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="4"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -4911,101 +4914,101 @@
   </r>
   <r>
     <s v="testcase execution1"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <n v="2"/>
-    <m/>
+    <n v="2"/>
   </r>
   <r>
     <s v="testcase execution2"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <n v="2"/>
-    <m/>
+    <n v="2"/>
   </r>
   <r>
     <s v="testcase execution3"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <n v="2"/>
-    <m/>
+    <n v="2"/>
   </r>
   <r>
     <s v="bug report 1"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <n v="2"/>
-    <m/>
+    <n v="2"/>
   </r>
   <r>
     <s v="bug report 2"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <n v="2"/>
-    <m/>
+    <n v="2"/>
   </r>
   <r>
     <s v="bug report 3"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <n v="2"/>
-    <m/>
+    <n v="2"/>
   </r>
   <r>
     <s v="rtm 1"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <n v="4"/>
-    <m/>
+    <n v="4"/>
   </r>
   <r>
     <s v="rtm 2"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <n v="4"/>
-    <m/>
+    <n v="4"/>
   </r>
   <r>
     <s v="rtm 3"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <n v="4"/>
-    <m/>
+    <n v="4"/>
   </r>
   <r>
     <s v="front - fix"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <n v="2"/>
-    <m/>
+    <n v="2"/>
   </r>
   <r>
     <s v="backend fix"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <n v="3"/>
-    <m/>
+    <n v="3"/>
   </r>
   <r>
     <s v="reviewing rtm"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <n v="3"/>
-    <m/>
+    <n v="3"/>
   </r>
   <r>
     <s v="exploratory session 1"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <n v="1"/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <s v="exploratory session 2"/>
-    <n v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="1"/>
   </r>
   <r>
     <m/>
@@ -5799,15 +5802,15 @@
       <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="87"/>
-      <c r="C12" s="87"/>
-      <c r="D12" s="87"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="87"/>
-      <c r="G12" s="88"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="86"/>
       <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6057,15 +6060,15 @@
       <c r="I26" s="10"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="86" t="s">
+      <c r="A27" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="87"/>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="88"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="86"/>
       <c r="I27" s="10"/>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8543,15 +8546,15 @@
       <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="87"/>
-      <c r="C13" s="87"/>
-      <c r="D13" s="87"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="88"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="86"/>
       <c r="I13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8633,15 +8636,15 @@
       <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="87"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="88"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="86"/>
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11299,15 +11302,15 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
       <c r="I12" s="35" t="s">
         <v>82</v>
       </c>
@@ -11702,15 +11705,15 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
       <c r="I28" s="35" t="s">
         <v>66</v>
       </c>
@@ -11966,7 +11969,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="91">
+      <c r="N43" s="95">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -11980,7 +11983,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="94">
+      <c r="R43" s="90">
         <f>SUM(O43:O50)</f>
         <v>24</v>
       </c>
@@ -11990,7 +11993,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="92"/>
+      <c r="N44" s="96"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O71" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>3</v>
@@ -12002,14 +12005,14 @@
         <f t="shared" ref="Q44:Q71" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alaaa</v>
       </c>
-      <c r="R44" s="94"/>
+      <c r="R44" s="90"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="92"/>
+      <c r="N45" s="96"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12021,14 +12024,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R45" s="94"/>
+      <c r="R45" s="90"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="92"/>
+      <c r="N46" s="96"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12040,14 +12043,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R46" s="94"/>
+      <c r="R46" s="90"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="92"/>
+      <c r="N47" s="96"/>
       <c r="O47" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12059,14 +12062,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R47" s="94"/>
+      <c r="R47" s="90"/>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="92"/>
+      <c r="N48" s="96"/>
       <c r="O48" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12078,14 +12081,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R48" s="94"/>
+      <c r="R48" s="90"/>
     </row>
     <row r="49" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="92"/>
+      <c r="N49" s="96"/>
       <c r="O49" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12097,14 +12100,14 @@
         <f t="shared" si="1"/>
         <v>Boda</v>
       </c>
-      <c r="R49" s="94"/>
+      <c r="R49" s="90"/>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
-      <c r="N50" s="93"/>
+      <c r="N50" s="97"/>
       <c r="O50" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12116,14 +12119,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R50" s="95"/>
+      <c r="R50" s="98"/>
     </row>
     <row r="51" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="91">
+      <c r="N51" s="95">
         <v>2</v>
       </c>
       <c r="O51" s="25">
@@ -12137,7 +12140,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R51" s="96">
+      <c r="R51" s="99">
         <f>SUM(O51:O52)</f>
         <v>4</v>
       </c>
@@ -12147,7 +12150,7 @@
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="92"/>
+      <c r="N52" s="96"/>
       <c r="O52" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12159,7 +12162,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R52" s="96"/>
+      <c r="R52" s="99"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
@@ -12190,7 +12193,7 @@
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="97">
+      <c r="N54" s="87">
         <v>4</v>
       </c>
       <c r="O54" s="25">
@@ -12204,7 +12207,7 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R54" s="99">
+      <c r="R54" s="89">
         <f>SUM(O54:O61)</f>
         <v>8</v>
       </c>
@@ -12214,7 +12217,7 @@
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="98"/>
+      <c r="N55" s="88"/>
       <c r="O55" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12226,14 +12229,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R55" s="94"/>
+      <c r="R55" s="90"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="98"/>
+      <c r="N56" s="88"/>
       <c r="O56" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12245,14 +12248,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R56" s="94"/>
+      <c r="R56" s="90"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="98"/>
+      <c r="N57" s="88"/>
       <c r="O57" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12264,14 +12267,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R57" s="94"/>
+      <c r="R57" s="90"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="98"/>
+      <c r="N58" s="88"/>
       <c r="O58" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12283,14 +12286,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R58" s="94"/>
+      <c r="R58" s="90"/>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="98"/>
+      <c r="N59" s="88"/>
       <c r="O59" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12302,14 +12305,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R59" s="94"/>
+      <c r="R59" s="90"/>
     </row>
     <row r="60" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="98"/>
+      <c r="N60" s="88"/>
       <c r="O60" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12321,14 +12324,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R60" s="94"/>
+      <c r="R60" s="90"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="98"/>
+      <c r="N61" s="88"/>
       <c r="O61" s="25">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -12340,14 +12343,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R61" s="100"/>
+      <c r="R61" s="91"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="97">
+      <c r="N62" s="87">
         <v>5</v>
       </c>
       <c r="O62" s="25">
@@ -12361,7 +12364,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R62" s="99">
+      <c r="R62" s="89">
         <f>SUM(O62:O66)</f>
         <v>12</v>
       </c>
@@ -12371,7 +12374,7 @@
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="98"/>
+      <c r="N63" s="88"/>
       <c r="O63" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12383,14 +12386,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R63" s="98"/>
+      <c r="R63" s="88"/>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="98"/>
+      <c r="N64" s="88"/>
       <c r="O64" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12402,14 +12405,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R64" s="98"/>
+      <c r="R64" s="88"/>
     </row>
     <row r="65" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="98"/>
+      <c r="N65" s="88"/>
       <c r="O65" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12421,14 +12424,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R65" s="98"/>
+      <c r="R65" s="88"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="101"/>
+      <c r="N66" s="92"/>
       <c r="O66" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12440,14 +12443,14 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R66" s="101"/>
+      <c r="R66" s="92"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="97">
+      <c r="N67" s="87">
         <v>6</v>
       </c>
       <c r="O67" s="25">
@@ -12461,7 +12464,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R67" s="99">
+      <c r="R67" s="89">
         <f>SUM(O67:O71)</f>
         <v>12</v>
       </c>
@@ -12471,7 +12474,7 @@
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="98"/>
+      <c r="N68" s="88"/>
       <c r="O68" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12483,14 +12486,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R68" s="98"/>
+      <c r="R68" s="88"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
-      <c r="N69" s="98"/>
+      <c r="N69" s="88"/>
       <c r="O69" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12502,14 +12505,14 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R69" s="98"/>
+      <c r="R69" s="88"/>
     </row>
     <row r="70" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="21"/>
       <c r="B70" s="21"/>
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
-      <c r="N70" s="98"/>
+      <c r="N70" s="88"/>
       <c r="O70" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12521,14 +12524,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R70" s="98"/>
+      <c r="R70" s="88"/>
     </row>
     <row r="71" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="21"/>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
-      <c r="N71" s="101"/>
+      <c r="N71" s="92"/>
       <c r="O71" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12540,7 +12543,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R71" s="101"/>
+      <c r="R71" s="92"/>
     </row>
     <row r="72" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
@@ -13512,18 +13515,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="N43:N50"/>
+    <mergeCell ref="R43:R50"/>
+    <mergeCell ref="N51:N52"/>
+    <mergeCell ref="R51:R52"/>
     <mergeCell ref="N54:N61"/>
     <mergeCell ref="R54:R61"/>
     <mergeCell ref="N62:N66"/>
     <mergeCell ref="R62:R66"/>
     <mergeCell ref="N67:N71"/>
     <mergeCell ref="R67:R71"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="N43:N50"/>
-    <mergeCell ref="R43:R50"/>
-    <mergeCell ref="N51:N52"/>
-    <mergeCell ref="R51:R52"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F14:F25 F30:F40" xr:uid="{AFC4AC33-7B9C-40BD-80E0-C1F9CEEBC5BF}">
@@ -13917,15 +13920,15 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
       <c r="I12" s="35" t="s">
         <v>121</v>
       </c>
@@ -14174,15 +14177,15 @@
       <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
       <c r="I28" s="35"/>
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
@@ -14406,7 +14409,7 @@
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="91">
+      <c r="N43" s="95">
         <v>1</v>
       </c>
       <c r="O43" s="25">
@@ -14420,7 +14423,7 @@
         <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
         <v>nabil</v>
       </c>
-      <c r="R43" s="94">
+      <c r="R43" s="90">
         <f>SUM(O43:O47)</f>
         <v>15</v>
       </c>
@@ -14430,7 +14433,7 @@
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="92"/>
+      <c r="N44" s="96"/>
       <c r="O44" s="25">
         <f t="shared" ref="O44:O68" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
         <v>3</v>
@@ -14442,14 +14445,14 @@
         <f t="shared" ref="Q44:Q68" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
         <v>alaaa</v>
       </c>
-      <c r="R44" s="94"/>
+      <c r="R44" s="90"/>
     </row>
     <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="92"/>
+      <c r="N45" s="96"/>
       <c r="O45" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14461,14 +14464,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R45" s="94"/>
+      <c r="R45" s="90"/>
     </row>
     <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="92"/>
+      <c r="N46" s="96"/>
       <c r="O46" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14480,14 +14483,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R46" s="94"/>
+      <c r="R46" s="90"/>
     </row>
     <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="92"/>
+      <c r="N47" s="96"/>
       <c r="O47" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14499,14 +14502,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R47" s="94"/>
+      <c r="R47" s="90"/>
     </row>
     <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="91">
+      <c r="N48" s="95">
         <v>2</v>
       </c>
       <c r="O48" s="25">
@@ -14520,7 +14523,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R48" s="96">
+      <c r="R48" s="99">
         <f>SUM(O48:O49)</f>
         <v>6</v>
       </c>
@@ -14530,7 +14533,7 @@
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="92"/>
+      <c r="N49" s="96"/>
       <c r="O49" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14542,7 +14545,7 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R49" s="96"/>
+      <c r="R49" s="99"/>
     </row>
     <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
@@ -14570,7 +14573,7 @@
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="97">
+      <c r="N51" s="87">
         <v>4</v>
       </c>
       <c r="O51" s="25" t="e">
@@ -14582,7 +14585,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R51" s="99">
+      <c r="R51" s="89">
         <v>0</v>
       </c>
     </row>
@@ -14591,7 +14594,7 @@
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="98"/>
+      <c r="N52" s="88"/>
       <c r="O52" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14601,14 +14604,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R52" s="94"/>
+      <c r="R52" s="90"/>
     </row>
     <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
-      <c r="N53" s="98"/>
+      <c r="N53" s="88"/>
       <c r="O53" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14618,14 +14621,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R53" s="94"/>
+      <c r="R53" s="90"/>
     </row>
     <row r="54" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="98"/>
+      <c r="N54" s="88"/>
       <c r="O54" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14635,14 +14638,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R54" s="94"/>
+      <c r="R54" s="90"/>
     </row>
     <row r="55" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="98"/>
+      <c r="N55" s="88"/>
       <c r="O55" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14652,14 +14655,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R55" s="94"/>
+      <c r="R55" s="90"/>
     </row>
     <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="98"/>
+      <c r="N56" s="88"/>
       <c r="O56" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14669,14 +14672,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R56" s="94"/>
+      <c r="R56" s="90"/>
     </row>
     <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="98"/>
+      <c r="N57" s="88"/>
       <c r="O57" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14686,14 +14689,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R57" s="94"/>
+      <c r="R57" s="90"/>
     </row>
     <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="98"/>
+      <c r="N58" s="88"/>
       <c r="O58" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14703,14 +14706,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R58" s="100"/>
+      <c r="R58" s="91"/>
     </row>
     <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="97">
+      <c r="N59" s="87">
         <v>5</v>
       </c>
       <c r="O59" s="25" t="e">
@@ -14722,7 +14725,7 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R59" s="99">
+      <c r="R59" s="89">
         <v>0</v>
       </c>
     </row>
@@ -14731,7 +14734,7 @@
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="98"/>
+      <c r="N60" s="88"/>
       <c r="O60" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14741,14 +14744,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R60" s="98"/>
+      <c r="R60" s="88"/>
     </row>
     <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="98"/>
+      <c r="N61" s="88"/>
       <c r="O61" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14758,14 +14761,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R61" s="98"/>
+      <c r="R61" s="88"/>
     </row>
     <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="98"/>
+      <c r="N62" s="88"/>
       <c r="O62" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14775,14 +14778,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R62" s="98"/>
+      <c r="R62" s="88"/>
     </row>
     <row r="63" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="101"/>
+      <c r="N63" s="92"/>
       <c r="O63" s="25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
@@ -14792,14 +14795,14 @@
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
-      <c r="R63" s="101"/>
+      <c r="R63" s="92"/>
     </row>
     <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="97">
+      <c r="N64" s="87">
         <v>6</v>
       </c>
       <c r="O64" s="25">
@@ -14813,7 +14816,7 @@
         <f t="shared" si="1"/>
         <v>alaaa</v>
       </c>
-      <c r="R64" s="99">
+      <c r="R64" s="89">
         <f>SUM(O64:O68)</f>
         <v>29</v>
       </c>
@@ -14823,7 +14826,7 @@
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="98"/>
+      <c r="N65" s="88"/>
       <c r="O65" s="25">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -14835,14 +14838,14 @@
         <f t="shared" si="1"/>
         <v>abdalrahman</v>
       </c>
-      <c r="R65" s="98"/>
+      <c r="R65" s="88"/>
     </row>
     <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="98"/>
+      <c r="N66" s="88"/>
       <c r="O66" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -14854,14 +14857,14 @@
         <f t="shared" si="1"/>
         <v>alhussin</v>
       </c>
-      <c r="R66" s="98"/>
+      <c r="R66" s="88"/>
     </row>
     <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="98"/>
+      <c r="N67" s="88"/>
       <c r="O67" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -14873,14 +14876,14 @@
         <f t="shared" si="1"/>
         <v>zahraan</v>
       </c>
-      <c r="R67" s="98"/>
+      <c r="R67" s="88"/>
     </row>
     <row r="68" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="N68" s="101"/>
+      <c r="N68" s="92"/>
       <c r="O68" s="25">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -14892,7 +14895,7 @@
         <f t="shared" si="1"/>
         <v>nabil</v>
       </c>
-      <c r="R68" s="101"/>
+      <c r="R68" s="92"/>
     </row>
     <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
@@ -15924,31 +15927,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="83" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="84" t="s">
+      <c r="J1" s="83" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="84" t="s">
+      <c r="L1" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="M1" s="84" t="s">
+      <c r="M1" s="83" t="s">
         <v>110</v>
       </c>
     </row>
@@ -16047,7 +16050,9 @@
       <c r="B5" s="67">
         <v>40</v>
       </c>
-      <c r="C5" s="57"/>
+      <c r="C5" s="57">
+        <v>26</v>
+      </c>
       <c r="D5" s="21"/>
       <c r="I5" s="35" t="s">
         <v>126</v>
@@ -16082,7 +16087,9 @@
       <c r="B6" s="67">
         <v>45</v>
       </c>
-      <c r="C6" s="57"/>
+      <c r="C6" s="57">
+        <v>32</v>
+      </c>
       <c r="D6" s="21"/>
       <c r="I6" s="35" t="s">
         <v>127</v>
@@ -16106,7 +16113,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="75">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16116,7 +16123,9 @@
       <c r="B7" s="61">
         <v>50</v>
       </c>
-      <c r="C7" s="57"/>
+      <c r="C7" s="57">
+        <v>50</v>
+      </c>
       <c r="D7" s="21"/>
       <c r="I7" s="35" t="s">
         <v>128</v>
@@ -16140,7 +16149,7 @@
         <v>10</v>
       </c>
       <c r="R7" s="78">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16152,7 +16161,7 @@
         <v>129</v>
       </c>
       <c r="J8" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="33" t="s">
         <v>103</v>
@@ -16160,7 +16169,9 @@
       <c r="L8" s="22">
         <v>2</v>
       </c>
-      <c r="M8" s="22"/>
+      <c r="M8" s="22">
+        <v>2</v>
+      </c>
       <c r="P8" s="76" t="s">
         <v>103</v>
       </c>
@@ -16168,7 +16179,7 @@
         <v>10</v>
       </c>
       <c r="R8" s="78">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16180,7 +16191,7 @@
         <v>130</v>
       </c>
       <c r="J9" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="33" t="s">
         <v>102</v>
@@ -16188,7 +16199,9 @@
       <c r="L9" s="22">
         <v>2</v>
       </c>
-      <c r="M9" s="22"/>
+      <c r="M9" s="22">
+        <v>2</v>
+      </c>
       <c r="P9" s="76" t="s">
         <v>97</v>
       </c>
@@ -16196,7 +16209,7 @@
         <v>10</v>
       </c>
       <c r="R9" s="78">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16208,7 +16221,7 @@
         <v>131</v>
       </c>
       <c r="J10" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="33" t="s">
         <v>101</v>
@@ -16216,7 +16229,9 @@
       <c r="L10" s="22">
         <v>2</v>
       </c>
-      <c r="M10" s="22"/>
+      <c r="M10" s="22">
+        <v>2</v>
+      </c>
       <c r="P10" s="76" t="s">
         <v>100</v>
       </c>
@@ -16224,7 +16239,7 @@
         <v>10</v>
       </c>
       <c r="R10" s="78">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16236,7 +16251,7 @@
         <v>132</v>
       </c>
       <c r="J11" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>102</v>
@@ -16244,7 +16259,9 @@
       <c r="L11" s="22">
         <v>2</v>
       </c>
-      <c r="M11" s="22"/>
+      <c r="M11" s="22">
+        <v>2</v>
+      </c>
       <c r="P11" s="76" t="s">
         <v>141</v>
       </c>
@@ -16252,20 +16269,20 @@
       <c r="R11" s="78"/>
     </row>
     <row r="12" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="89" t="s">
+      <c r="A12" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
       <c r="I12" s="35" t="s">
         <v>133</v>
       </c>
       <c r="J12" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="33" t="s">
         <v>103</v>
@@ -16273,7 +16290,9 @@
       <c r="L12" s="22">
         <v>2</v>
       </c>
-      <c r="M12" s="22"/>
+      <c r="M12" s="22">
+        <v>2</v>
+      </c>
       <c r="P12" s="79" t="s">
         <v>104</v>
       </c>
@@ -16281,7 +16300,7 @@
         <v>50</v>
       </c>
       <c r="R12" s="81">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -16310,7 +16329,7 @@
         <v>134</v>
       </c>
       <c r="J13" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="33" t="s">
         <v>101</v>
@@ -16318,11 +16337,13 @@
       <c r="L13" s="22">
         <v>2</v>
       </c>
-      <c r="M13" s="22"/>
+      <c r="M13" s="22">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="22"/>
-      <c r="B14" s="83"/>
+      <c r="B14" s="82"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
@@ -16332,7 +16353,7 @@
         <v>135</v>
       </c>
       <c r="J14" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>102</v>
@@ -16340,7 +16361,9 @@
       <c r="L14" s="22">
         <v>4</v>
       </c>
-      <c r="M14" s="22"/>
+      <c r="M14" s="22">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="22"/>
@@ -16354,7 +16377,7 @@
         <v>136</v>
       </c>
       <c r="J15" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="33" t="s">
         <v>103</v>
@@ -16362,7 +16385,9 @@
       <c r="L15" s="22">
         <v>4</v>
       </c>
-      <c r="M15" s="22"/>
+      <c r="M15" s="22">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:28" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="22"/>
@@ -16376,7 +16401,7 @@
         <v>137</v>
       </c>
       <c r="J16" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="33" t="s">
         <v>101</v>
@@ -16384,7 +16409,9 @@
       <c r="L16" s="22">
         <v>4</v>
       </c>
-      <c r="M16" s="22"/>
+      <c r="M16" s="22">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22"/>
@@ -16398,7 +16425,7 @@
         <v>138</v>
       </c>
       <c r="J17" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="33" t="s">
         <v>100</v>
@@ -16406,7 +16433,9 @@
       <c r="L17" s="22">
         <v>2</v>
       </c>
-      <c r="M17" s="22"/>
+      <c r="M17" s="22">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="22"/>
@@ -16420,7 +16449,7 @@
         <v>139</v>
       </c>
       <c r="J18" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="33" t="s">
         <v>97</v>
@@ -16428,7 +16457,9 @@
       <c r="L18" s="22">
         <v>3</v>
       </c>
-      <c r="M18" s="22"/>
+      <c r="M18" s="22">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="32"/>
@@ -16442,7 +16473,7 @@
         <v>140</v>
       </c>
       <c r="J19" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="33" t="s">
         <v>100</v>
@@ -16450,7 +16481,9 @@
       <c r="L19" s="22">
         <v>3</v>
       </c>
-      <c r="M19" s="22"/>
+      <c r="M19" s="22">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="32"/>
@@ -16464,7 +16497,7 @@
         <v>144</v>
       </c>
       <c r="J20" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="33" t="s">
         <v>100</v>
@@ -16472,7 +16505,9 @@
       <c r="L20" s="22">
         <v>1</v>
       </c>
-      <c r="M20" s="22"/>
+      <c r="M20" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32"/>
@@ -16486,7 +16521,7 @@
         <v>145</v>
       </c>
       <c r="J21" s="43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="33" t="s">
         <v>97</v>
@@ -16494,7 +16529,9 @@
       <c r="L21" s="22">
         <v>1</v>
       </c>
-      <c r="M21" s="22"/>
+      <c r="M21" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="32"/>
@@ -16575,15 +16612,15 @@
       <c r="M27" s="22"/>
     </row>
     <row r="28" spans="1:13" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="89" t="s">
+      <c r="A28" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="90"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="90"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="90"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
       <c r="I28" s="35"/>
       <c r="J28" s="43"/>
       <c r="K28" s="43"/>
@@ -16623,7 +16660,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="52"/>
-      <c r="C30" s="83">
+      <c r="C30" s="82">
         <v>5</v>
       </c>
       <c r="D30" s="50">
@@ -16674,7 +16711,7 @@
       <c r="L32" s="22"/>
       <c r="M32" s="22"/>
     </row>
-    <row r="33" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="41"/>
       <c r="B33" s="40"/>
       <c r="C33" s="32"/>
@@ -16688,7 +16725,7 @@
       <c r="L33" s="22"/>
       <c r="M33" s="22"/>
     </row>
-    <row r="34" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="32"/>
       <c r="B34" s="32"/>
       <c r="C34" s="37"/>
@@ -16702,7 +16739,7 @@
       <c r="L34" s="22"/>
       <c r="M34" s="22"/>
     </row>
-    <row r="35" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="32"/>
       <c r="B35" s="32"/>
       <c r="C35" s="32"/>
@@ -16716,7 +16753,7 @@
       <c r="L35" s="22"/>
       <c r="M35" s="22"/>
     </row>
-    <row r="36" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="32"/>
       <c r="B36" s="32"/>
       <c r="C36" s="32"/>
@@ -16730,7 +16767,7 @@
       <c r="L36" s="22"/>
       <c r="M36" s="22"/>
     </row>
-    <row r="37" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="32"/>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
@@ -16747,10 +16784,10 @@
       </c>
       <c r="M37" s="22">
         <f>SUM(M2:M36)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="32"/>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
@@ -16759,7 +16796,7 @@
       <c r="F38" s="32"/>
       <c r="G38" s="32"/>
     </row>
-    <row r="39" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
       <c r="B39" s="32"/>
       <c r="C39" s="32"/>
@@ -16768,7 +16805,7 @@
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
     </row>
-    <row r="40" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="32"/>
       <c r="B40" s="32"/>
       <c r="C40" s="32"/>
@@ -16777,578 +16814,465 @@
       <c r="F40" s="32"/>
       <c r="G40" s="32"/>
     </row>
-    <row r="41" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="21"/>
       <c r="B41" s="21"/>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
-    </row>
-    <row r="42" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M41" s="100"/>
+      <c r="N41" s="100"/>
+      <c r="O41" s="100"/>
+      <c r="P41" s="100"/>
+      <c r="Q41" s="100"/>
+      <c r="R41" s="100"/>
+      <c r="S41" s="100"/>
+      <c r="T41" s="100"/>
+    </row>
+    <row r="42" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="21"/>
       <c r="B42" s="21"/>
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
-      <c r="N42" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="O42" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="P42" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q42" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="R42" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M42" s="100"/>
+      <c r="N42" s="100"/>
+      <c r="O42" s="100"/>
+      <c r="P42" s="100"/>
+      <c r="Q42" s="100"/>
+      <c r="R42" s="100"/>
+      <c r="S42" s="100"/>
+      <c r="T42" s="100"/>
+    </row>
+    <row r="43" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="21"/>
       <c r="B43" s="21"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
-      <c r="N43" s="91">
-        <v>1</v>
-      </c>
-      <c r="O43" s="25">
-        <f>VLOOKUP(P43,$I$2:$L$36,4,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="P43" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q43" s="24" t="str">
-        <f>VLOOKUP(P43,$I$2:$L$36,3,FALSE)</f>
-        <v>nabil</v>
-      </c>
-      <c r="R43" s="94">
-        <f>SUM(O43:O46)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M43" s="100"/>
+      <c r="N43" s="100"/>
+      <c r="O43" s="100"/>
+      <c r="P43" s="100"/>
+      <c r="Q43" s="100"/>
+      <c r="R43" s="100"/>
+      <c r="S43" s="100"/>
+      <c r="T43" s="100"/>
+    </row>
+    <row r="44" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="21"/>
       <c r="B44" s="21"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
-      <c r="N44" s="92"/>
-      <c r="O44" s="25">
-        <f t="shared" ref="O44:O67" si="0">VLOOKUP(P44,$I$3:$L$36,4,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="P44" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q44" s="24" t="str">
-        <f t="shared" ref="Q44:Q67" si="1">VLOOKUP(P44,$I$3:$L$36,3,FALSE)</f>
-        <v>alhussin</v>
-      </c>
-      <c r="R44" s="94"/>
-    </row>
-    <row r="45" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M44" s="100"/>
+      <c r="N44" s="100"/>
+      <c r="O44" s="100"/>
+      <c r="P44" s="100"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="100"/>
+      <c r="S44" s="100"/>
+      <c r="T44" s="100"/>
+    </row>
+    <row r="45" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
-      <c r="N45" s="92"/>
-      <c r="O45" s="25">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="P45" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q45" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>abdalrahman</v>
-      </c>
-      <c r="R45" s="94"/>
-    </row>
-    <row r="46" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M45" s="100"/>
+      <c r="N45" s="100"/>
+      <c r="O45" s="100"/>
+      <c r="P45" s="100"/>
+      <c r="Q45" s="100"/>
+      <c r="R45" s="100"/>
+      <c r="S45" s="100"/>
+      <c r="T45" s="100"/>
+    </row>
+    <row r="46" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="21"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
-      <c r="N46" s="92"/>
-      <c r="O46" s="25">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="P46" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q46" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>alaaa</v>
-      </c>
-      <c r="R46" s="94"/>
-    </row>
-    <row r="47" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M46" s="100"/>
+      <c r="N46" s="100"/>
+      <c r="O46" s="100"/>
+      <c r="P46" s="100"/>
+      <c r="Q46" s="100"/>
+      <c r="R46" s="100"/>
+      <c r="S46" s="100"/>
+      <c r="T46" s="100"/>
+    </row>
+    <row r="47" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
-      <c r="N47" s="91">
-        <v>2</v>
-      </c>
-      <c r="O47" s="25">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="P47" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q47" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>zahraan</v>
-      </c>
-      <c r="R47" s="96">
-        <f>SUM(O47:O48)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M47" s="100"/>
+      <c r="N47" s="100"/>
+      <c r="O47" s="100"/>
+      <c r="P47" s="100"/>
+      <c r="Q47" s="100"/>
+      <c r="R47" s="100"/>
+      <c r="S47" s="100"/>
+      <c r="T47" s="100"/>
+    </row>
+    <row r="48" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="21"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
-      <c r="N48" s="92"/>
-      <c r="O48" s="25">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="P48" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q48" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>nabil</v>
-      </c>
-      <c r="R48" s="96"/>
-    </row>
-    <row r="49" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M48" s="100"/>
+      <c r="N48" s="100"/>
+      <c r="O48" s="100"/>
+      <c r="P48" s="100"/>
+      <c r="Q48" s="100"/>
+      <c r="R48" s="100"/>
+      <c r="S48" s="100"/>
+      <c r="T48" s="100"/>
+    </row>
+    <row r="49" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="21"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
-      <c r="N49" s="85">
-        <v>3</v>
-      </c>
-      <c r="O49" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P49" s="24"/>
-      <c r="Q49" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R49" s="82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M49" s="100"/>
+      <c r="N49" s="100"/>
+      <c r="O49" s="100"/>
+      <c r="P49" s="100"/>
+      <c r="Q49" s="100"/>
+      <c r="R49" s="100"/>
+      <c r="S49" s="100"/>
+      <c r="T49" s="100"/>
+    </row>
+    <row r="50" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
-      <c r="N50" s="97">
-        <v>4</v>
-      </c>
-      <c r="O50" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P50" s="24"/>
-      <c r="Q50" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R50" s="99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M50" s="100"/>
+      <c r="N50" s="100"/>
+      <c r="O50" s="100"/>
+      <c r="P50" s="100"/>
+      <c r="Q50" s="100"/>
+      <c r="R50" s="100"/>
+      <c r="S50" s="100"/>
+      <c r="T50" s="100"/>
+    </row>
+    <row r="51" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21"/>
       <c r="B51" s="21"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
-      <c r="N51" s="98"/>
-      <c r="O51" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P51" s="24"/>
-      <c r="Q51" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R51" s="94"/>
-    </row>
-    <row r="52" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M51" s="100"/>
+      <c r="N51" s="100"/>
+      <c r="O51" s="100"/>
+      <c r="P51" s="100"/>
+      <c r="Q51" s="100"/>
+      <c r="R51" s="100"/>
+      <c r="S51" s="100"/>
+      <c r="T51" s="100"/>
+    </row>
+    <row r="52" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="21"/>
       <c r="B52" s="21"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
-      <c r="N52" s="98"/>
-      <c r="O52" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R52" s="94"/>
-    </row>
-    <row r="53" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="100"/>
+      <c r="N52" s="100"/>
+      <c r="O52" s="100"/>
+      <c r="P52" s="100"/>
+      <c r="Q52" s="100"/>
+      <c r="R52" s="100"/>
+      <c r="S52" s="100"/>
+      <c r="T52" s="100"/>
+    </row>
+    <row r="53" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="21"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
-      <c r="N53" s="98"/>
-      <c r="O53" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P53" s="24"/>
-      <c r="Q53" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R53" s="94"/>
-    </row>
-    <row r="54" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M53" s="100"/>
+      <c r="N53" s="100"/>
+      <c r="O53" s="100"/>
+      <c r="P53" s="100"/>
+      <c r="Q53" s="100"/>
+      <c r="R53" s="100"/>
+      <c r="S53" s="100"/>
+      <c r="T53" s="100"/>
+    </row>
+    <row r="54" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
-      <c r="N54" s="98"/>
-      <c r="O54" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P54" s="24"/>
-      <c r="Q54" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R54" s="94"/>
-    </row>
-    <row r="55" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M54" s="100"/>
+      <c r="N54" s="100"/>
+      <c r="O54" s="100"/>
+      <c r="P54" s="100"/>
+      <c r="Q54" s="100"/>
+      <c r="R54" s="100"/>
+      <c r="S54" s="100"/>
+      <c r="T54" s="100"/>
+    </row>
+    <row r="55" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
-      <c r="N55" s="98"/>
-      <c r="O55" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P55" s="24"/>
-      <c r="Q55" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R55" s="94"/>
-    </row>
-    <row r="56" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M55" s="100"/>
+      <c r="N55" s="100"/>
+      <c r="O55" s="100"/>
+      <c r="P55" s="100"/>
+      <c r="Q55" s="100"/>
+      <c r="R55" s="100"/>
+      <c r="S55" s="100"/>
+      <c r="T55" s="100"/>
+    </row>
+    <row r="56" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="21"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
-      <c r="N56" s="98"/>
-      <c r="O56" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P56" s="24"/>
-      <c r="Q56" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R56" s="94"/>
-    </row>
-    <row r="57" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M56" s="100"/>
+      <c r="N56" s="100"/>
+      <c r="O56" s="100"/>
+      <c r="P56" s="100"/>
+      <c r="Q56" s="100"/>
+      <c r="R56" s="100"/>
+      <c r="S56" s="100"/>
+      <c r="T56" s="100"/>
+    </row>
+    <row r="57" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="21"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
-      <c r="N57" s="98"/>
-      <c r="O57" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P57" s="24"/>
-      <c r="Q57" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
+      <c r="M57" s="100"/>
+      <c r="N57" s="100"/>
+      <c r="O57" s="100"/>
+      <c r="P57" s="100"/>
+      <c r="Q57" s="100"/>
       <c r="R57" s="100"/>
-    </row>
-    <row r="58" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S57" s="100"/>
+      <c r="T57" s="100"/>
+    </row>
+    <row r="58" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="21"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
-      <c r="N58" s="97">
-        <v>5</v>
-      </c>
-      <c r="O58" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P58" s="24"/>
-      <c r="Q58" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R58" s="99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M58" s="100"/>
+      <c r="N58" s="100"/>
+      <c r="O58" s="100"/>
+      <c r="P58" s="100"/>
+      <c r="Q58" s="100"/>
+      <c r="R58" s="100"/>
+      <c r="S58" s="100"/>
+      <c r="T58" s="100"/>
+    </row>
+    <row r="59" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="21"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
-      <c r="N59" s="98"/>
-      <c r="O59" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P59" s="24"/>
-      <c r="Q59" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R59" s="98"/>
-    </row>
-    <row r="60" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M59" s="100"/>
+      <c r="N59" s="100"/>
+      <c r="O59" s="100"/>
+      <c r="P59" s="100"/>
+      <c r="Q59" s="100"/>
+      <c r="R59" s="100"/>
+      <c r="S59" s="100"/>
+      <c r="T59" s="100"/>
+    </row>
+    <row r="60" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="21"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
-      <c r="N60" s="98"/>
-      <c r="O60" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P60" s="24"/>
-      <c r="Q60" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R60" s="98"/>
-    </row>
-    <row r="61" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M60" s="100"/>
+      <c r="N60" s="100"/>
+      <c r="O60" s="100"/>
+      <c r="P60" s="100"/>
+      <c r="Q60" s="100"/>
+      <c r="R60" s="100"/>
+      <c r="S60" s="100"/>
+      <c r="T60" s="100"/>
+    </row>
+    <row r="61" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
-      <c r="N61" s="98"/>
-      <c r="O61" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R61" s="98"/>
-    </row>
-    <row r="62" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M61" s="100"/>
+      <c r="N61" s="100"/>
+      <c r="O61" s="100"/>
+      <c r="P61" s="100"/>
+      <c r="Q61" s="100"/>
+      <c r="R61" s="100"/>
+      <c r="S61" s="100"/>
+      <c r="T61" s="100"/>
+    </row>
+    <row r="62" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="21"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
-      <c r="N62" s="101"/>
-      <c r="O62" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P62" s="24"/>
-      <c r="Q62" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R62" s="101"/>
-    </row>
-    <row r="63" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M62" s="100"/>
+      <c r="N62" s="100"/>
+      <c r="O62" s="100"/>
+      <c r="P62" s="100"/>
+      <c r="Q62" s="100"/>
+      <c r="R62" s="100"/>
+      <c r="S62" s="100"/>
+      <c r="T62" s="100"/>
+    </row>
+    <row r="63" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="21"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
-      <c r="N63" s="97">
-        <v>6</v>
-      </c>
-      <c r="O63" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P63" s="35"/>
-      <c r="Q63" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R63" s="99" t="e">
-        <f>SUM(O63:O67)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M63" s="100"/>
+      <c r="N63" s="100"/>
+      <c r="O63" s="100"/>
+      <c r="P63" s="100"/>
+      <c r="Q63" s="100"/>
+      <c r="R63" s="100"/>
+      <c r="S63" s="100"/>
+      <c r="T63" s="100"/>
+    </row>
+    <row r="64" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="21"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
-      <c r="N64" s="98"/>
-      <c r="O64" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P64" s="35"/>
-      <c r="Q64" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R64" s="98"/>
-    </row>
-    <row r="65" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M64" s="100"/>
+      <c r="N64" s="100"/>
+      <c r="O64" s="100"/>
+      <c r="P64" s="100"/>
+      <c r="Q64" s="100"/>
+      <c r="R64" s="100"/>
+      <c r="S64" s="100"/>
+      <c r="T64" s="100"/>
+    </row>
+    <row r="65" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="21"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
-      <c r="N65" s="98"/>
-      <c r="O65" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P65" s="35"/>
-      <c r="Q65" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R65" s="98"/>
-    </row>
-    <row r="66" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M65" s="100"/>
+      <c r="N65" s="100"/>
+      <c r="O65" s="100"/>
+      <c r="P65" s="100"/>
+      <c r="Q65" s="100"/>
+      <c r="R65" s="100"/>
+      <c r="S65" s="100"/>
+      <c r="T65" s="100"/>
+    </row>
+    <row r="66" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="21"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
-      <c r="N66" s="98"/>
-      <c r="O66" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P66" s="35"/>
-      <c r="Q66" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R66" s="98"/>
-    </row>
-    <row r="67" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M66" s="100"/>
+      <c r="N66" s="100"/>
+      <c r="O66" s="100"/>
+      <c r="P66" s="100"/>
+      <c r="Q66" s="100"/>
+      <c r="R66" s="100"/>
+      <c r="S66" s="100"/>
+      <c r="T66" s="100"/>
+    </row>
+    <row r="67" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="21"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="N67" s="101"/>
-      <c r="O67" s="25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P67" s="35"/>
-      <c r="Q67" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R67" s="101"/>
-    </row>
-    <row r="68" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M67" s="100"/>
+      <c r="N67" s="100"/>
+      <c r="O67" s="100"/>
+      <c r="P67" s="100"/>
+      <c r="Q67" s="100"/>
+      <c r="R67" s="100"/>
+      <c r="S67" s="100"/>
+      <c r="T67" s="100"/>
+    </row>
+    <row r="68" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
       <c r="B68" s="21"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="P68" s="24"/>
-      <c r="Q68" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="R68" s="22" t="e">
-        <f>SUM(R43:R67)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M68" s="100"/>
+      <c r="N68" s="100"/>
+      <c r="O68" s="100"/>
+      <c r="P68" s="100"/>
+      <c r="Q68" s="100"/>
+      <c r="R68" s="100"/>
+      <c r="S68" s="100"/>
+      <c r="T68" s="100"/>
+    </row>
+    <row r="69" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
       <c r="B69" s="21"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
     </row>
-    <row r="70" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="21"/>
       <c r="B70" s="21"/>
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
     </row>
-    <row r="71" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="21"/>
       <c r="B71" s="21"/>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
     </row>
-    <row r="72" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
       <c r="B72" s="21"/>
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
     </row>
-    <row r="73" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="21"/>
       <c r="B73" s="21"/>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
     </row>
-    <row r="74" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="21"/>
       <c r="B74" s="21"/>
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
     </row>
-    <row r="75" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="21"/>
       <c r="B75" s="21"/>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
     </row>
-    <row r="76" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="21"/>
       <c r="B76" s="21"/>
       <c r="C76" s="21"/>
       <c r="D76" s="21"/>
     </row>
-    <row r="77" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="21"/>
       <c r="B77" s="21"/>
       <c r="C77" s="21"/>
       <c r="D77" s="21"/>
     </row>
-    <row r="78" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="21"/>
       <c r="B78" s="21"/>
       <c r="C78" s="21"/>
       <c r="D78" s="21"/>
     </row>
-    <row r="79" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="21"/>
       <c r="B79" s="21"/>
       <c r="C79" s="21"/>
       <c r="D79" s="21"/>
     </row>
-    <row r="80" spans="1:18" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="21"/>
       <c r="B80" s="21"/>
       <c r="C80" s="21"/>
@@ -18237,28 +18161,18 @@
       <c r="D227" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="N50:N57"/>
-    <mergeCell ref="R50:R57"/>
-    <mergeCell ref="N58:N62"/>
-    <mergeCell ref="R58:R62"/>
-    <mergeCell ref="N63:N67"/>
-    <mergeCell ref="R63:R67"/>
+  <mergeCells count="2">
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="N43:N46"/>
-    <mergeCell ref="R43:R46"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="R47:R48"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F14:F25 F30:F40" xr:uid="{67546FD1-F383-41E0-BB8B-2F4BEECE4BCF}">
       <formula1>"Avoid,Mitigate,Accept"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>